--- a/grupos/5ARHV - Estadisticos 20221.xlsx
+++ b/grupos/5ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="172">
   <si>
     <t>Materia</t>
   </si>
@@ -323,217 +323,217 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>FERNANDEZ</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>VERGEL</t>
+  </si>
+  <si>
+    <t>TANIA</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>CONSUELO DALILA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>VALENTIN</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>SANDY SAMARA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>TAILY</t>
+  </si>
+  <si>
+    <t>INGRID YALITH</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>DIANA VIANNEY</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>JARED JESUS</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>QUIAHUA</t>
   </si>
   <si>
     <t>PAZOS</t>
   </si>
   <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
-    <t>TANIA</t>
-  </si>
-  <si>
-    <t>AMYRA NAHOMY</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>VALENTIN</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>IVAN DE JESUS</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
-    <t>INGRID YALITH</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>DIANA VIANNEY</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
+    <t>LORENA</t>
   </si>
   <si>
     <t>CARLA DANIELA</t>
-  </si>
-  <si>
-    <t>JARED JESUS</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>LORENA</t>
   </si>
 </sst>
 </file>
@@ -1566,7 +1566,7 @@
         <v>-1</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1620,7 +1620,7 @@
         <v>-1</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2182,7 +2182,7 @@
         <v>-1</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2236,7 +2236,7 @@
         <v>-1</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -3561,7 +3561,7 @@
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H39">
         <v>-1</v>
@@ -3615,7 +3615,7 @@
         <v>-1</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3626,7 +3626,7 @@
         <v>8</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
         <v>-1</v>
@@ -3644,7 +3644,7 @@
         <v>8</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3928,25 +3928,25 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3988,7 +3988,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4023,10 +4023,10 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4043,10 +4043,10 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4066,7 +4066,7 @@
         <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4083,10 +4083,10 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4103,10 +4103,10 @@
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -4126,7 +4126,7 @@
         <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4143,10 +4143,10 @@
         <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4163,10 +4163,10 @@
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -4183,10 +4183,10 @@
         <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4203,10 +4203,10 @@
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -4223,10 +4223,10 @@
         <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -4243,10 +4243,10 @@
         <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4263,10 +4263,10 @@
         <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -4283,10 +4283,10 @@
         <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -4303,36 +4303,36 @@
         <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920122</v>
+        <v>20330051920123</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
         <v>109</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4343,21 +4343,21 @@
         <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920123</v>
+        <v>20330051920124</v>
       </c>
       <c r="B19" t="s">
         <v>77</v>
@@ -4366,13 +4366,13 @@
         <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4383,16 +4383,16 @@
         <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4403,13 +4403,13 @@
         <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
         <v>61</v>
@@ -4417,22 +4417,22 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920124</v>
+        <v>20330051920125</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4446,13 +4446,13 @@
         <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4466,10 +4466,10 @@
         <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
         <v>61</v>
@@ -4477,22 +4477,22 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920125</v>
+        <v>20330051920126</v>
       </c>
       <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
         <v>78</v>
       </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
       <c r="D25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4506,13 +4506,13 @@
         <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4526,13 +4526,13 @@
         <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4546,10 +4546,10 @@
         <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
         <v>61</v>
@@ -4557,22 +4557,22 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920126</v>
+        <v>20330051920127</v>
       </c>
       <c r="B29" t="s">
         <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4586,13 +4586,13 @@
         <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4606,10 +4606,10 @@
         <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
         <v>61</v>
@@ -4617,22 +4617,22 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920127</v>
+        <v>20330051920128</v>
       </c>
       <c r="B32" t="s">
         <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4643,36 +4643,36 @@
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920128</v>
+        <v>20330051920129</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s">
         <v>112</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4683,16 +4683,16 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D35" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -4703,16 +4703,16 @@
         <v>80</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D36" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4723,16 +4723,16 @@
         <v>80</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D37" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4743,36 +4743,36 @@
         <v>80</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D38" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920129</v>
+        <v>20330051920131</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s">
         <v>113</v>
       </c>
       <c r="D39" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4783,16 +4783,16 @@
         <v>81</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D40" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -4803,13 +4803,13 @@
         <v>81</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D41" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E41" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F41" t="s">
         <v>61</v>
@@ -4817,42 +4817,42 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920131</v>
+        <v>20330051920132</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C42" t="s">
         <v>114</v>
       </c>
       <c r="D42" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920131</v>
+        <v>20330051920132</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s">
         <v>114</v>
       </c>
       <c r="D43" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E43" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4863,16 +4863,16 @@
         <v>82</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4883,21 +4883,21 @@
         <v>82</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E45" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920132</v>
+        <v>20330051920133</v>
       </c>
       <c r="B46" t="s">
         <v>82</v>
@@ -4906,18 +4906,18 @@
         <v>115</v>
       </c>
       <c r="D46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E46" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920132</v>
+        <v>20330051920133</v>
       </c>
       <c r="B47" t="s">
         <v>82</v>
@@ -4926,10 +4926,10 @@
         <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F47" t="s">
         <v>61</v>
@@ -4943,53 +4943,53 @@
         <v>82</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E48" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920133</v>
+        <v>20330051920134</v>
       </c>
       <c r="B49" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C49" t="s">
         <v>116</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E49" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>20330051920133</v>
+        <v>20330051920134</v>
       </c>
       <c r="B50" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C50" t="s">
         <v>116</v>
       </c>
       <c r="D50" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F50" t="s">
         <v>61</v>
@@ -5003,53 +5003,53 @@
         <v>83</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E51" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>20330051920134</v>
+        <v>20330051920135</v>
       </c>
       <c r="B52" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
         <v>117</v>
       </c>
       <c r="D52" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>20330051920134</v>
+        <v>20330051920135</v>
       </c>
       <c r="B53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C53" t="s">
         <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F53" t="s">
         <v>61</v>
@@ -5063,16 +5063,16 @@
         <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E54" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -5083,13 +5083,13 @@
         <v>84</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D55" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E55" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F55" t="s">
         <v>61</v>
@@ -5097,39 +5097,39 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>20330051920135</v>
+        <v>20330051920136</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="D56" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E56" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>20330051920135</v>
+        <v>20330051920136</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="D57" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E57" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F57" t="s">
         <v>61</v>
@@ -5146,13 +5146,13 @@
         <v>88</v>
       </c>
       <c r="D58" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E58" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -5166,10 +5166,10 @@
         <v>88</v>
       </c>
       <c r="D59" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E59" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
         <v>61</v>
@@ -5177,39 +5177,39 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>20330051920136</v>
+        <v>20330051920137</v>
       </c>
       <c r="B60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E60" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>20330051920136</v>
+        <v>20330051920137</v>
       </c>
       <c r="B61" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C61" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F61" t="s">
         <v>61</v>
@@ -5223,30 +5223,30 @@
         <v>86</v>
       </c>
       <c r="C62" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E62" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>20330051920137</v>
+        <v>19330051920383</v>
       </c>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C63" t="s">
         <v>119</v>
       </c>
       <c r="D63" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E63" t="s">
         <v>7</v>
@@ -5257,16 +5257,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>20330051920137</v>
+        <v>19330051920383</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C64" t="s">
         <v>119</v>
       </c>
       <c r="D64" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
@@ -5277,36 +5277,36 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>19330051920383</v>
+        <v>20330051920139</v>
       </c>
       <c r="B65" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C65" t="s">
         <v>120</v>
       </c>
       <c r="D65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E65" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>19330051920383</v>
+        <v>20330051920139</v>
       </c>
       <c r="B66" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C66" t="s">
         <v>120</v>
       </c>
       <c r="D66" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E66" t="s">
         <v>9</v>
@@ -5317,16 +5317,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>20330051920139</v>
+        <v>19330051920387</v>
       </c>
       <c r="B67" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C67" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="D67" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5337,16 +5337,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>20330051920139</v>
+        <v>19330051920387</v>
       </c>
       <c r="B68" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C68" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="D68" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E68" t="s">
         <v>9</v>
@@ -5357,16 +5357,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>19330051920387</v>
+        <v>20330051920140</v>
       </c>
       <c r="B69" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C69" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="D69" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -5377,19 +5377,19 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>19330051920387</v>
+        <v>20330051920140</v>
       </c>
       <c r="B70" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C70" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="D70" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E70" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F70" t="s">
         <v>61</v>
@@ -5403,53 +5403,53 @@
         <v>90</v>
       </c>
       <c r="C71" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D71" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E71" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>20330051920140</v>
+        <v>20330051920141</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D72" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E72" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>20330051920140</v>
+        <v>20330051920141</v>
       </c>
       <c r="B73" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C73" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D73" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E73" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F73" t="s">
         <v>61</v>
@@ -5463,53 +5463,53 @@
         <v>91</v>
       </c>
       <c r="C74" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D74" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E74" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F74" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>20330051920141</v>
+        <v>20330051920389</v>
       </c>
       <c r="B75" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C75" t="s">
         <v>122</v>
       </c>
       <c r="D75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E75" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
-        <v>20330051920141</v>
+        <v>20330051920389</v>
       </c>
       <c r="B76" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C76" t="s">
         <v>122</v>
       </c>
       <c r="D76" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E76" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F76" t="s">
         <v>61</v>
@@ -5523,44 +5523,44 @@
         <v>92</v>
       </c>
       <c r="C77" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D77" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E77" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78">
-        <v>20330051920389</v>
+        <v>20330051920142</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C78" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D78" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E78" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79">
-        <v>20330051920389</v>
+        <v>20330051920143</v>
       </c>
       <c r="B79" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C79" t="s">
         <v>123</v>
@@ -5569,21 +5569,21 @@
         <v>159</v>
       </c>
       <c r="E79" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80">
-        <v>20330051920142</v>
+        <v>20330051920144</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C80" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D80" t="s">
         <v>160</v>
@@ -5597,36 +5597,36 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81">
-        <v>20330051920143</v>
+        <v>20330051920144</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C81" t="s">
         <v>124</v>
       </c>
       <c r="D81" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E81" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F81" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82">
-        <v>20330051920144</v>
+        <v>20330051920387</v>
       </c>
       <c r="B82" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C82" t="s">
         <v>125</v>
       </c>
       <c r="D82" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5637,16 +5637,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83">
-        <v>20330051920144</v>
+        <v>20330051920387</v>
       </c>
       <c r="B83" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C83" t="s">
         <v>125</v>
       </c>
       <c r="D83" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E83" t="s">
         <v>7</v>
@@ -5663,53 +5663,53 @@
         <v>96</v>
       </c>
       <c r="C84" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D84" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E84" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F84" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85">
-        <v>20330051920387</v>
+        <v>20330051920148</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C85" t="s">
         <v>126</v>
       </c>
       <c r="D85" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E85" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86">
-        <v>20330051920387</v>
+        <v>20330051920148</v>
       </c>
       <c r="B86" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C86" t="s">
         <v>126</v>
       </c>
       <c r="D86" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E86" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F86" t="s">
         <v>61</v>
@@ -5723,76 +5723,76 @@
         <v>97</v>
       </c>
       <c r="C87" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D87" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E87" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F87" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88">
-        <v>20330051920148</v>
+        <v>20330051920150</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C88" t="s">
         <v>127</v>
       </c>
       <c r="D88" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E88" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89">
-        <v>20330051920148</v>
+        <v>20330051920151</v>
       </c>
       <c r="B89" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C89" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D89" t="s">
         <v>163</v>
       </c>
       <c r="E89" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90">
-        <v>20330051920150</v>
+        <v>20330051920151</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C90" t="s">
         <v>128</v>
       </c>
       <c r="D90" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E90" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F90" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -5803,70 +5803,61 @@
         <v>99</v>
       </c>
       <c r="C91" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D91" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E91" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F91" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92">
-        <v>20330051920151</v>
+        <v>20330051920153</v>
       </c>
       <c r="B92" t="s">
-        <v>99</v>
-      </c>
-      <c r="C92" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="D92" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E92" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F92" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93">
-        <v>20330051920151</v>
+        <v>20330051920153</v>
       </c>
       <c r="B93" t="s">
-        <v>99</v>
-      </c>
-      <c r="C93" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="D93" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E93" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F93" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94">
-        <v>20330051920151</v>
+        <v>20330051920153</v>
       </c>
       <c r="B94" t="s">
-        <v>99</v>
-      </c>
-      <c r="C94" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="D94" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E94" t="s">
         <v>9</v>
@@ -5877,50 +5868,59 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95">
-        <v>20330051920153</v>
+        <v>19330051920145</v>
       </c>
       <c r="B95" t="s">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="C95" t="s">
+        <v>129</v>
       </c>
       <c r="D95" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E95" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F95" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96">
-        <v>20330051920153</v>
+        <v>19330051920145</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="C96" t="s">
+        <v>129</v>
       </c>
       <c r="D96" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E96" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F96" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97">
-        <v>20330051920153</v>
+        <v>19330051920145</v>
       </c>
       <c r="B97" t="s">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="C97" t="s">
+        <v>129</v>
       </c>
       <c r="D97" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E97" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F97" t="s">
         <v>61</v>
@@ -5928,141 +5928,61 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98">
-        <v>18330051920189</v>
+        <v>19330051920145</v>
       </c>
       <c r="B98" t="s">
         <v>101</v>
       </c>
       <c r="C98" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D98" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E98" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F98" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99">
-        <v>19330051920145</v>
+        <v>19330051920399</v>
       </c>
       <c r="B99" t="s">
         <v>102</v>
       </c>
       <c r="C99" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D99" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E99" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F99" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100">
-        <v>19330051920145</v>
+        <v>19330051920399</v>
       </c>
       <c r="B100" t="s">
         <v>102</v>
       </c>
       <c r="C100" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D100" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E100" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F100" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>19330051920145</v>
-      </c>
-      <c r="B101" t="s">
-        <v>102</v>
-      </c>
-      <c r="C101" t="s">
-        <v>131</v>
-      </c>
-      <c r="D101" t="s">
-        <v>168</v>
-      </c>
-      <c r="E101" t="s">
-        <v>7</v>
-      </c>
-      <c r="F101" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>19330051920145</v>
-      </c>
-      <c r="B102" t="s">
-        <v>102</v>
-      </c>
-      <c r="C102" t="s">
-        <v>131</v>
-      </c>
-      <c r="D102" t="s">
-        <v>168</v>
-      </c>
-      <c r="E102" t="s">
-        <v>9</v>
-      </c>
-      <c r="F102" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>19330051920399</v>
-      </c>
-      <c r="B103" t="s">
-        <v>103</v>
-      </c>
-      <c r="C103" t="s">
-        <v>132</v>
-      </c>
-      <c r="D103" t="s">
-        <v>169</v>
-      </c>
-      <c r="E103" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>19330051920399</v>
-      </c>
-      <c r="B104" t="s">
-        <v>103</v>
-      </c>
-      <c r="C104" t="s">
-        <v>132</v>
-      </c>
-      <c r="D104" t="s">
-        <v>169</v>
-      </c>
-      <c r="E104" t="s">
-        <v>9</v>
-      </c>
-      <c r="F104" t="s">
         <v>61</v>
       </c>
     </row>
@@ -6099,16 +6019,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920122</v>
+        <v>20330051920129</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -6116,19 +6036,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920129</v>
+        <v>20330051920122</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6142,7 +6062,7 @@
         <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -6150,16 +6070,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920131</v>
+        <v>20330051920132</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
         <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -6167,16 +6087,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920132</v>
+        <v>20330051920135</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -6184,16 +6104,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920135</v>
+        <v>20330051920136</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -6201,16 +6121,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920136</v>
+        <v>19330051920145</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -6218,50 +6138,50 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920151</v>
+        <v>19330051920427</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920145</v>
+        <v>20330051920124</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920427</v>
+        <v>20330051920125</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -6269,16 +6189,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920124</v>
+        <v>20330051920127</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -6286,16 +6206,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920125</v>
+        <v>20330051920131</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -6303,16 +6223,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920127</v>
+        <v>20330051920133</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -6320,16 +6240,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920133</v>
+        <v>20330051920134</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
         <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -6337,13 +6257,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920134</v>
+        <v>20330051920137</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
         <v>151</v>
@@ -6354,16 +6274,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920137</v>
+        <v>20330051920140</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -6371,16 +6291,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920140</v>
+        <v>20330051920141</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -6388,16 +6308,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920141</v>
+        <v>20330051920389</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
         <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -6405,16 +6325,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920389</v>
+        <v>20330051920387</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -6422,16 +6342,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920387</v>
+        <v>20330051920148</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
         <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -6439,13 +6359,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920148</v>
+        <v>20330051920151</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
         <v>163</v>
@@ -6462,7 +6382,7 @@
         <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -6476,10 +6396,10 @@
         <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -6493,10 +6413,10 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E25">
         <v>2</v>
@@ -6510,10 +6430,10 @@
         <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E26">
         <v>2</v>
@@ -6527,10 +6447,10 @@
         <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -6544,10 +6464,10 @@
         <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -6561,10 +6481,10 @@
         <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -6581,7 +6501,7 @@
         <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E30">
         <v>2</v>
@@ -6595,10 +6515,10 @@
         <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E31">
         <v>2</v>
@@ -6609,13 +6529,13 @@
         <v>19330051920399</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E32">
         <v>2</v>
@@ -6629,10 +6549,10 @@
         <v>69</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -6646,10 +6566,10 @@
         <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -6666,7 +6586,7 @@
         <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -6683,7 +6603,7 @@
         <v>78</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -6697,10 +6617,10 @@
         <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -6714,10 +6634,10 @@
         <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -6731,10 +6651,10 @@
         <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D39" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6742,30 +6662,30 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>18330051920189</v>
+        <v>18330051920185</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C40" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="D40" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>18330051920185</v>
+        <v>18330051920189</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="C41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D41" t="s">
         <v>171</v>
@@ -6781,7 +6701,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6819,10 +6739,10 @@
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -6842,10 +6762,10 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6865,10 +6785,10 @@
         <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -6888,10 +6808,10 @@
         <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -6911,10 +6831,10 @@
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6934,10 +6854,10 @@
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -6957,10 +6877,10 @@
         <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -6980,10 +6900,10 @@
         <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -7003,10 +6923,10 @@
         <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -7026,10 +6946,10 @@
         <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -7052,7 +6972,7 @@
         <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -7075,7 +6995,7 @@
         <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -7095,10 +7015,10 @@
         <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -7118,10 +7038,10 @@
         <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -7138,13 +7058,13 @@
         <v>19330051920399</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -7161,13 +7081,13 @@
         <v>19330051920399</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -7187,10 +7107,10 @@
         <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -7213,7 +7133,7 @@
         <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -7236,7 +7156,7 @@
         <v>78</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -7256,10 +7176,10 @@
         <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -7279,10 +7199,10 @@
         <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -7291,29 +7211,6 @@
         <v>60</v>
       </c>
       <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>18330051920189</v>
-      </c>
-      <c r="B23" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" t="s">
-        <v>130</v>
-      </c>
-      <c r="D23" t="s">
-        <v>167</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20221.xlsx
+++ b/grupos/5ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="172">
   <si>
     <t>Materia</t>
   </si>
@@ -200,18 +200,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
@@ -233,304 +233,304 @@
     <t>BRETON</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>FERNANDEZ</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>VERGEL</t>
+  </si>
+  <si>
+    <t>TANIA</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>VALENTIN</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>SANDY SAMARA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>TAILY</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>JARED JESUS</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
     <t>CASTELLANOS</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>CONGUILLO</t>
   </si>
   <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>TIBURCIO</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
+    <t>VERA</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>RAMON</t>
+    <t>QUIAHUA</t>
   </si>
   <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
-    <t>TANIA</t>
-  </si>
-  <si>
-    <t>AMYRA NAHOMY</t>
+    <t>PAZOS</t>
   </si>
   <si>
     <t>MELANIE NAOMI</t>
   </si>
   <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
     <t>CONSUELO DALILA</t>
   </si>
   <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>VALENTIN</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>IVAN DE JESUS</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
     <t>INGRID YALITH</t>
   </si>
   <si>
     <t>LUCERO</t>
   </si>
   <si>
-    <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
+    <t>LORENA</t>
   </si>
   <si>
     <t>DIANA VIANNEY</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>JARED JESUS</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>PAZOS</t>
-  </si>
-  <si>
-    <t>LORENA</t>
   </si>
   <si>
     <t>CARLA DANIELA</t>
@@ -1098,7 +1098,7 @@
         <v>6</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -1152,7 +1152,7 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>-1</v>
@@ -1175,7 +1175,7 @@
         <v>7</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>8</v>
@@ -1229,7 +1229,7 @@
         <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1252,7 +1252,7 @@
         <v>7</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F8">
         <v>8</v>
@@ -1306,7 +1306,7 @@
         <v>7</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1329,7 +1329,7 @@
         <v>-1</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F9">
         <v>7</v>
@@ -1383,7 +1383,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1406,7 +1406,7 @@
         <v>-1</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F10">
         <v>7</v>
@@ -1460,7 +1460,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1637,7 +1637,7 @@
         <v>6</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -1691,7 +1691,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>-1</v>
@@ -1714,7 +1714,7 @@
         <v>-1</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -1768,7 +1768,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>-1</v>
@@ -1791,7 +1791,7 @@
         <v>-1</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -1845,7 +1845,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>-1</v>
@@ -1945,7 +1945,7 @@
         <v>-1</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -1999,7 +1999,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>-1</v>
@@ -2022,7 +2022,7 @@
         <v>6</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -2076,7 +2076,7 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>-1</v>
@@ -2176,7 +2176,7 @@
         <v>-1</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>-1</v>
@@ -2230,7 +2230,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>-1</v>
@@ -2330,7 +2330,7 @@
         <v>-1</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -2384,7 +2384,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>-1</v>
@@ -2407,7 +2407,7 @@
         <v>-1</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -2461,7 +2461,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>-1</v>
@@ -2484,7 +2484,7 @@
         <v>-1</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F24">
         <v>-1</v>
@@ -2538,7 +2538,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>-1</v>
@@ -2561,7 +2561,7 @@
         <v>-1</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>-1</v>
@@ -2615,7 +2615,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>-1</v>
@@ -2638,7 +2638,7 @@
         <v>-1</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F26">
         <v>-1</v>
@@ -2692,7 +2692,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>-1</v>
@@ -2756,7 +2756,7 @@
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F28">
         <v>-1</v>
@@ -2810,7 +2810,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>-1</v>
@@ -2833,7 +2833,7 @@
         <v>-1</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F29">
         <v>-1</v>
@@ -2887,7 +2887,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>-1</v>
@@ -2910,7 +2910,7 @@
         <v>7</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <v>-1</v>
@@ -2964,7 +2964,7 @@
         <v>7</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>-1</v>
@@ -2987,7 +2987,7 @@
         <v>-1</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F31">
         <v>-1</v>
@@ -3041,7 +3041,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>-1</v>
@@ -3064,7 +3064,7 @@
         <v>-1</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F32">
         <v>-1</v>
@@ -3118,7 +3118,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>-1</v>
@@ -3141,7 +3141,7 @@
         <v>10</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F33">
         <v>10</v>
@@ -3195,7 +3195,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3218,7 +3218,7 @@
         <v>7</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F34">
         <v>8</v>
@@ -3272,7 +3272,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>8</v>
@@ -3295,7 +3295,7 @@
         <v>-1</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F35">
         <v>-1</v>
@@ -3349,7 +3349,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>-1</v>
@@ -3401,7 +3401,7 @@
         <v>-1</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F37">
         <v>-1</v>
@@ -3455,7 +3455,7 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>-1</v>
@@ -3478,7 +3478,7 @@
         <v>9</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F38">
         <v>8</v>
@@ -3532,7 +3532,7 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X38">
         <v>8</v>
@@ -3794,159 +3794,162 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
+      </c>
       <c r="I2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>30.56</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>75</v>
+        <v>69.44</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D4">
+        <v>17</v>
+      </c>
+      <c r="E4">
         <v>11</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
       <c r="F4">
-        <v>30.56</v>
+        <v>50</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>32.35</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>69.44</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G5">
-        <v>32.35</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>17.65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3988,7 +3991,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4023,16 +4026,16 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4043,33 +4046,33 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920115</v>
+        <v>20330051920116</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>60</v>
@@ -4077,19 +4080,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920116</v>
+        <v>20330051920121</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>60</v>
@@ -4097,39 +4100,39 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920116</v>
+        <v>19330051920427</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920118</v>
+        <v>19330051920427</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>60</v>
@@ -4137,19 +4140,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920121</v>
+        <v>19330051920427</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>60</v>
@@ -4157,99 +4160,99 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920121</v>
+        <v>20330051920122</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920427</v>
+        <v>20330051920122</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920427</v>
+        <v>20330051920122</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920427</v>
+        <v>20330051920122</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920122</v>
+        <v>20330051920123</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>60</v>
@@ -4257,79 +4260,79 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920122</v>
+        <v>20330051920124</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920122</v>
+        <v>20330051920124</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920122</v>
+        <v>20330051920125</v>
       </c>
       <c r="B16" t="s">
         <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920123</v>
+        <v>20330051920125</v>
       </c>
       <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
         <v>77</v>
       </c>
-      <c r="C17" t="s">
-        <v>109</v>
-      </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
         <v>60</v>
@@ -4337,99 +4340,99 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920123</v>
+        <v>20330051920126</v>
       </c>
       <c r="B18" t="s">
         <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920124</v>
+        <v>20330051920126</v>
       </c>
       <c r="B19" t="s">
         <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920124</v>
+        <v>20330051920126</v>
       </c>
       <c r="B20" t="s">
         <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920124</v>
+        <v>20330051920126</v>
       </c>
       <c r="B21" t="s">
         <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920125</v>
+        <v>20330051920127</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
         <v>60</v>
@@ -4437,139 +4440,139 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920125</v>
+        <v>20330051920127</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920125</v>
+        <v>20330051920128</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920126</v>
+        <v>20330051920129</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920126</v>
+        <v>20330051920129</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920126</v>
+        <v>20330051920129</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920126</v>
+        <v>20330051920129</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920127</v>
+        <v>20330051920129</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
         <v>60</v>
@@ -4577,79 +4580,79 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920127</v>
+        <v>20330051920131</v>
       </c>
       <c r="B30" t="s">
         <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920127</v>
+        <v>20330051920131</v>
       </c>
       <c r="B31" t="s">
         <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920128</v>
+        <v>20330051920132</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920128</v>
+        <v>20330051920132</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
         <v>61</v>
@@ -4657,19 +4660,19 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920129</v>
+        <v>20330051920132</v>
       </c>
       <c r="B34" t="s">
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
         <v>60</v>
@@ -4677,99 +4680,99 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920129</v>
+        <v>20330051920132</v>
       </c>
       <c r="B35" t="s">
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E35" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920129</v>
+        <v>20330051920133</v>
       </c>
       <c r="B36" t="s">
         <v>80</v>
       </c>
       <c r="C36" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920129</v>
+        <v>20330051920133</v>
       </c>
       <c r="B37" t="s">
         <v>80</v>
       </c>
       <c r="C37" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920129</v>
+        <v>20330051920134</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920131</v>
+        <v>20330051920134</v>
       </c>
       <c r="B39" t="s">
         <v>81</v>
       </c>
       <c r="C39" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D39" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
         <v>60</v>
@@ -4777,59 +4780,59 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920131</v>
+        <v>20330051920135</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D40" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E40" t="s">
         <v>7</v>
       </c>
       <c r="F40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920131</v>
+        <v>20330051920135</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920132</v>
+        <v>20330051920135</v>
       </c>
       <c r="B42" t="s">
         <v>82</v>
       </c>
       <c r="C42" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
         <v>60</v>
@@ -4837,79 +4840,79 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920132</v>
+        <v>20330051920136</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D43" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920132</v>
+        <v>20330051920136</v>
       </c>
       <c r="B44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D44" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E44" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920132</v>
+        <v>20330051920136</v>
       </c>
       <c r="B45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D45" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920133</v>
+        <v>20330051920137</v>
       </c>
       <c r="B46" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D46" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F46" t="s">
         <v>60</v>
@@ -4917,59 +4920,59 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920133</v>
+        <v>20330051920137</v>
       </c>
       <c r="B47" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D47" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>20330051920133</v>
+        <v>19330051920383</v>
       </c>
       <c r="B48" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D48" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920134</v>
+        <v>19330051920383</v>
       </c>
       <c r="B49" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D49" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E49" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="s">
         <v>60</v>
@@ -4977,59 +4980,59 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>20330051920134</v>
+        <v>20330051920139</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D50" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E50" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>20330051920134</v>
+        <v>19330051920387</v>
       </c>
       <c r="B51" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="D51" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E51" t="s">
         <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>20330051920135</v>
+        <v>20330051920140</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D52" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F52" t="s">
         <v>60</v>
@@ -5037,79 +5040,79 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>20330051920135</v>
+        <v>20330051920140</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D53" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>20330051920135</v>
+        <v>20330051920141</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F54" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>20330051920135</v>
+        <v>20330051920141</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C55" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D55" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
       </c>
       <c r="F55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>20330051920136</v>
+        <v>20330051920389</v>
       </c>
       <c r="B56" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C56" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D56" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F56" t="s">
         <v>60</v>
@@ -5117,79 +5120,79 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>20330051920136</v>
+        <v>20330051920389</v>
       </c>
       <c r="B57" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C57" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D57" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E57" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>20330051920136</v>
+        <v>20330051920144</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C58" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F58" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>20330051920136</v>
+        <v>20330051920387</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C59" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="D59" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E59" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>20330051920137</v>
+        <v>20330051920387</v>
       </c>
       <c r="B60" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D60" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E60" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F60" t="s">
         <v>60</v>
@@ -5197,79 +5200,79 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>20330051920137</v>
+        <v>20330051920148</v>
       </c>
       <c r="B61" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C61" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D61" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E61" t="s">
         <v>7</v>
       </c>
       <c r="F61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>20330051920137</v>
+        <v>20330051920148</v>
       </c>
       <c r="B62" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D62" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>19330051920383</v>
+        <v>20330051920151</v>
       </c>
       <c r="B63" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C63" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D63" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E63" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>19330051920383</v>
+        <v>20330051920151</v>
       </c>
       <c r="B64" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D64" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E64" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F64" t="s">
         <v>61</v>
@@ -5277,19 +5280,19 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>20330051920139</v>
+        <v>20330051920151</v>
       </c>
       <c r="B65" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C65" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D65" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E65" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F65" t="s">
         <v>60</v>
@@ -5297,39 +5300,33 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>20330051920139</v>
+        <v>20330051920153</v>
       </c>
       <c r="B66" t="s">
-        <v>88</v>
-      </c>
-      <c r="C66" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="D66" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E66" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>19330051920387</v>
+        <v>20330051920153</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
-      </c>
-      <c r="C67" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D67" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E67" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F67" t="s">
         <v>60</v>
@@ -5337,653 +5334,122 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>19330051920387</v>
+        <v>19330051920145</v>
       </c>
       <c r="B68" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="D68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E68" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F68" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>20330051920140</v>
+        <v>19330051920145</v>
       </c>
       <c r="B69" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C69" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D69" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E69" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>20330051920140</v>
+        <v>19330051920145</v>
       </c>
       <c r="B70" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C70" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D70" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E70" t="s">
         <v>7</v>
       </c>
       <c r="F70" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>20330051920140</v>
+        <v>19330051920145</v>
       </c>
       <c r="B71" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C71" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D71" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>20330051920141</v>
+        <v>19330051920399</v>
       </c>
       <c r="B72" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C72" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D72" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E72" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F72" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>20330051920141</v>
+        <v>19330051920399</v>
       </c>
       <c r="B73" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C73" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D73" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E73" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920141</v>
-      </c>
-      <c r="B74" t="s">
-        <v>91</v>
-      </c>
-      <c r="C74" t="s">
-        <v>121</v>
-      </c>
-      <c r="D74" t="s">
-        <v>156</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>20330051920389</v>
-      </c>
-      <c r="B75" t="s">
-        <v>92</v>
-      </c>
-      <c r="C75" t="s">
-        <v>122</v>
-      </c>
-      <c r="D75" t="s">
-        <v>157</v>
-      </c>
-      <c r="E75" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>20330051920389</v>
-      </c>
-      <c r="B76" t="s">
-        <v>92</v>
-      </c>
-      <c r="C76" t="s">
-        <v>122</v>
-      </c>
-      <c r="D76" t="s">
-        <v>157</v>
-      </c>
-      <c r="E76" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>20330051920389</v>
-      </c>
-      <c r="B77" t="s">
-        <v>92</v>
-      </c>
-      <c r="C77" t="s">
-        <v>122</v>
-      </c>
-      <c r="D77" t="s">
-        <v>157</v>
-      </c>
-      <c r="E77" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>20330051920142</v>
-      </c>
-      <c r="B78" t="s">
-        <v>93</v>
-      </c>
-      <c r="C78" t="s">
-        <v>115</v>
-      </c>
-      <c r="D78" t="s">
-        <v>158</v>
-      </c>
-      <c r="E78" t="s">
-        <v>8</v>
-      </c>
-      <c r="F78" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>20330051920143</v>
-      </c>
-      <c r="B79" t="s">
-        <v>94</v>
-      </c>
-      <c r="C79" t="s">
-        <v>123</v>
-      </c>
-      <c r="D79" t="s">
-        <v>159</v>
-      </c>
-      <c r="E79" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>20330051920144</v>
-      </c>
-      <c r="B80" t="s">
-        <v>95</v>
-      </c>
-      <c r="C80" t="s">
-        <v>124</v>
-      </c>
-      <c r="D80" t="s">
-        <v>160</v>
-      </c>
-      <c r="E80" t="s">
-        <v>8</v>
-      </c>
-      <c r="F80" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>20330051920144</v>
-      </c>
-      <c r="B81" t="s">
-        <v>95</v>
-      </c>
-      <c r="C81" t="s">
-        <v>124</v>
-      </c>
-      <c r="D81" t="s">
-        <v>160</v>
-      </c>
-      <c r="E81" t="s">
-        <v>7</v>
-      </c>
-      <c r="F81" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>20330051920387</v>
-      </c>
-      <c r="B82" t="s">
-        <v>96</v>
-      </c>
-      <c r="C82" t="s">
-        <v>125</v>
-      </c>
-      <c r="D82" t="s">
-        <v>155</v>
-      </c>
-      <c r="E82" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>20330051920387</v>
-      </c>
-      <c r="B83" t="s">
-        <v>96</v>
-      </c>
-      <c r="C83" t="s">
-        <v>125</v>
-      </c>
-      <c r="D83" t="s">
-        <v>155</v>
-      </c>
-      <c r="E83" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>20330051920387</v>
-      </c>
-      <c r="B84" t="s">
-        <v>96</v>
-      </c>
-      <c r="C84" t="s">
-        <v>125</v>
-      </c>
-      <c r="D84" t="s">
-        <v>155</v>
-      </c>
-      <c r="E84" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>20330051920148</v>
-      </c>
-      <c r="B85" t="s">
-        <v>97</v>
-      </c>
-      <c r="C85" t="s">
-        <v>126</v>
-      </c>
-      <c r="D85" t="s">
-        <v>161</v>
-      </c>
-      <c r="E85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>20330051920148</v>
-      </c>
-      <c r="B86" t="s">
-        <v>97</v>
-      </c>
-      <c r="C86" t="s">
-        <v>126</v>
-      </c>
-      <c r="D86" t="s">
-        <v>161</v>
-      </c>
-      <c r="E86" t="s">
-        <v>7</v>
-      </c>
-      <c r="F86" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>20330051920148</v>
-      </c>
-      <c r="B87" t="s">
-        <v>97</v>
-      </c>
-      <c r="C87" t="s">
-        <v>126</v>
-      </c>
-      <c r="D87" t="s">
-        <v>161</v>
-      </c>
-      <c r="E87" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>20330051920150</v>
-      </c>
-      <c r="B88" t="s">
-        <v>98</v>
-      </c>
-      <c r="C88" t="s">
-        <v>127</v>
-      </c>
-      <c r="D88" t="s">
-        <v>162</v>
-      </c>
-      <c r="E88" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>20330051920151</v>
-      </c>
-      <c r="B89" t="s">
-        <v>99</v>
-      </c>
-      <c r="C89" t="s">
-        <v>128</v>
-      </c>
-      <c r="D89" t="s">
-        <v>163</v>
-      </c>
-      <c r="E89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>20330051920151</v>
-      </c>
-      <c r="B90" t="s">
-        <v>99</v>
-      </c>
-      <c r="C90" t="s">
-        <v>128</v>
-      </c>
-      <c r="D90" t="s">
-        <v>163</v>
-      </c>
-      <c r="E90" t="s">
-        <v>6</v>
-      </c>
-      <c r="F90" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>20330051920151</v>
-      </c>
-      <c r="B91" t="s">
-        <v>99</v>
-      </c>
-      <c r="C91" t="s">
-        <v>128</v>
-      </c>
-      <c r="D91" t="s">
-        <v>163</v>
-      </c>
-      <c r="E91" t="s">
-        <v>9</v>
-      </c>
-      <c r="F91" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>20330051920153</v>
-      </c>
-      <c r="B92" t="s">
-        <v>100</v>
-      </c>
-      <c r="D92" t="s">
-        <v>164</v>
-      </c>
-      <c r="E92" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>20330051920153</v>
-      </c>
-      <c r="B93" t="s">
-        <v>100</v>
-      </c>
-      <c r="D93" t="s">
-        <v>164</v>
-      </c>
-      <c r="E93" t="s">
-        <v>7</v>
-      </c>
-      <c r="F93" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>20330051920153</v>
-      </c>
-      <c r="B94" t="s">
-        <v>100</v>
-      </c>
-      <c r="D94" t="s">
-        <v>164</v>
-      </c>
-      <c r="E94" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>19330051920145</v>
-      </c>
-      <c r="B95" t="s">
-        <v>101</v>
-      </c>
-      <c r="C95" t="s">
-        <v>129</v>
-      </c>
-      <c r="D95" t="s">
-        <v>165</v>
-      </c>
-      <c r="E95" t="s">
-        <v>5</v>
-      </c>
-      <c r="F95" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>19330051920145</v>
-      </c>
-      <c r="B96" t="s">
-        <v>101</v>
-      </c>
-      <c r="C96" t="s">
-        <v>129</v>
-      </c>
-      <c r="D96" t="s">
-        <v>165</v>
-      </c>
-      <c r="E96" t="s">
-        <v>6</v>
-      </c>
-      <c r="F96" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>19330051920145</v>
-      </c>
-      <c r="B97" t="s">
-        <v>101</v>
-      </c>
-      <c r="C97" t="s">
-        <v>129</v>
-      </c>
-      <c r="D97" t="s">
-        <v>165</v>
-      </c>
-      <c r="E97" t="s">
-        <v>7</v>
-      </c>
-      <c r="F97" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>19330051920145</v>
-      </c>
-      <c r="B98" t="s">
-        <v>101</v>
-      </c>
-      <c r="C98" t="s">
-        <v>129</v>
-      </c>
-      <c r="D98" t="s">
-        <v>165</v>
-      </c>
-      <c r="E98" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>19330051920399</v>
-      </c>
-      <c r="B99" t="s">
-        <v>102</v>
-      </c>
-      <c r="C99" t="s">
-        <v>130</v>
-      </c>
-      <c r="D99" t="s">
-        <v>166</v>
-      </c>
-      <c r="E99" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>19330051920399</v>
-      </c>
-      <c r="B100" t="s">
-        <v>102</v>
-      </c>
-      <c r="C100" t="s">
-        <v>130</v>
-      </c>
-      <c r="D100" t="s">
-        <v>166</v>
-      </c>
-      <c r="E100" t="s">
-        <v>9</v>
-      </c>
-      <c r="F100" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -6022,13 +5488,13 @@
         <v>20330051920129</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -6039,13 +5505,13 @@
         <v>20330051920122</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -6056,13 +5522,13 @@
         <v>20330051920126</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -6073,13 +5539,13 @@
         <v>20330051920132</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -6087,16 +5553,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920135</v>
+        <v>19330051920145</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -6104,50 +5570,50 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920136</v>
+        <v>19330051920427</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920145</v>
+        <v>20330051920135</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920427</v>
+        <v>20330051920136</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -6155,16 +5621,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920124</v>
+        <v>20330051920151</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -6172,234 +5638,234 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920125</v>
+        <v>20330051920124</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920127</v>
+        <v>20330051920125</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920131</v>
+        <v>20330051920127</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920133</v>
+        <v>20330051920131</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920134</v>
+        <v>20330051920133</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920137</v>
+        <v>20330051920134</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920140</v>
+        <v>20330051920137</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920141</v>
+        <v>19330051920383</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920389</v>
+        <v>20330051920140</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920387</v>
+        <v>20330051920141</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920148</v>
+        <v>20330051920389</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920151</v>
+        <v>20330051920387</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920153</v>
+        <v>20330051920148</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920116</v>
+        <v>20330051920153</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -6407,16 +5873,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920121</v>
+        <v>19330051920399</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="D25" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="E25">
         <v>2</v>
@@ -6424,135 +5890,135 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920123</v>
+        <v>18330051920393</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920128</v>
+        <v>19330051920360</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920383</v>
+        <v>20330051920116</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920139</v>
+        <v>20330051920121</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920387</v>
+        <v>20330051920123</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920144</v>
+        <v>20330051920128</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920399</v>
+        <v>20330051920139</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>18330051920393</v>
+        <v>19330051920387</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -6560,16 +6026,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920360</v>
+        <v>20330051920144</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -6580,16 +6046,16 @@
         <v>20330051920115</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D35" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -6597,16 +6063,16 @@
         <v>20330051920118</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6614,16 +6080,16 @@
         <v>20330051920142</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6631,44 +6097,44 @@
         <v>20330051920143</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>158</v>
       </c>
       <c r="C38" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="D38" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>20330051920150</v>
+        <v>18330051920185</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="D39" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>18330051920185</v>
+        <v>20330051920150</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="C40" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D40" t="s">
         <v>170</v>
@@ -6682,10 +6148,10 @@
         <v>18330051920189</v>
       </c>
       <c r="B41" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C41" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D41" t="s">
         <v>171</v>
@@ -6701,7 +6167,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6739,16 +6205,16 @@
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -6762,16 +6228,16 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6779,42 +6245,42 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920121</v>
+        <v>20330051920116</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>61</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920121</v>
+        <v>20330051920116</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>60</v>
@@ -6825,45 +6291,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920128</v>
+        <v>20330051920123</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920128</v>
+        <v>20330051920123</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6871,22 +6337,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920383</v>
+        <v>20330051920125</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -6894,22 +6360,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920383</v>
+        <v>20330051920125</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -6917,19 +6383,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920139</v>
+        <v>20330051920127</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>60</v>
@@ -6940,22 +6406,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920139</v>
+        <v>20330051920127</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6963,19 +6429,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920387</v>
+        <v>20330051920131</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>60</v>
@@ -6986,22 +6452,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920387</v>
+        <v>20330051920131</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -7009,42 +6475,42 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920143</v>
+        <v>20330051920134</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920143</v>
+        <v>20330051920134</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
         <v>60</v>
@@ -7055,22 +6521,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920399</v>
+        <v>20330051920137</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -7078,22 +6544,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920399</v>
+        <v>20330051920137</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -7101,22 +6567,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>18330051920393</v>
+        <v>19330051920383</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -7124,19 +6590,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920115</v>
+        <v>19330051920383</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
         <v>60</v>
@@ -7147,19 +6613,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920118</v>
+        <v>20330051920141</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
         <v>60</v>
@@ -7170,19 +6636,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920142</v>
+        <v>20330051920141</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
         <v>60</v>
@@ -7193,25 +6659,370 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920150</v>
+        <v>20330051920389</v>
       </c>
       <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" t="s">
+        <v>148</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920389</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" t="s">
+        <v>148</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920144</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E24" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" t="s">
+        <v>61</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920144</v>
+      </c>
+      <c r="B25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>60</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920387</v>
+      </c>
+      <c r="B26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920387</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D27" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920148</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920148</v>
+      </c>
+      <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>19330051920399</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" t="s">
+        <v>154</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>19330051920399</v>
+      </c>
+      <c r="B31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" t="s">
+        <v>154</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>18330051920393</v>
+      </c>
+      <c r="B32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" t="s">
         <v>98</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D32" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920121</v>
+      </c>
+      <c r="B33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" t="s">
         <v>127</v>
       </c>
-      <c r="D22" t="s">
-        <v>162</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" t="s">
+        <v>60</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>20330051920128</v>
+      </c>
+      <c r="B34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>60</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>20330051920139</v>
+      </c>
+      <c r="B35" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>60</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>19330051920387</v>
+      </c>
+      <c r="B36" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>60</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>20330051920143</v>
+      </c>
+      <c r="B37" t="s">
+        <v>158</v>
+      </c>
+      <c r="C37" t="s">
+        <v>161</v>
+      </c>
+      <c r="D37" t="s">
+        <v>168</v>
+      </c>
+      <c r="E37" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ARHV - Estadisticos 20221.xlsx
+++ b/grupos/5ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="172">
   <si>
     <t>Materia</t>
   </si>
@@ -1034,7 +1034,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1069,7 +1069,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1107,7 +1107,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1143,7 +1143,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -1184,7 +1184,7 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1199,7 +1199,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1220,7 +1220,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -1235,7 +1235,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1261,7 +1261,7 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1276,7 +1276,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1338,7 +1338,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1353,7 +1353,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1374,7 +1374,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1415,7 +1415,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1430,7 +1430,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1451,7 +1451,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1466,7 +1466,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1492,7 +1492,7 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1507,7 +1507,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1528,7 +1528,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>5</v>
@@ -1569,7 +1569,7 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1584,7 +1584,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1605,7 +1605,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1646,7 +1646,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1661,7 +1661,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1682,7 +1682,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1723,7 +1723,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1738,7 +1738,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1759,7 +1759,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -1774,7 +1774,7 @@
         <v>-1</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1815,7 +1815,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1836,7 +1836,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -1877,7 +1877,7 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1913,7 +1913,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -1954,7 +1954,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -1990,7 +1990,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -2031,7 +2031,7 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2046,7 +2046,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2067,7 +2067,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -2105,10 +2105,10 @@
         <v>-1</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2123,7 +2123,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2144,7 +2144,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2159,7 +2159,7 @@
         <v>-1</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2185,7 +2185,7 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2200,7 +2200,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2221,7 +2221,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2262,7 +2262,7 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2339,7 +2339,7 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2354,7 +2354,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2375,7 +2375,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2390,7 +2390,7 @@
         <v>-1</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2413,10 +2413,10 @@
         <v>-1</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2431,7 +2431,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2452,7 +2452,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>5</v>
@@ -2467,7 +2467,7 @@
         <v>-1</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2490,10 +2490,10 @@
         <v>-1</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2529,7 +2529,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -2544,7 +2544,7 @@
         <v>-1</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2570,7 +2570,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2585,7 +2585,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2606,7 +2606,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -2621,7 +2621,7 @@
         <v>-1</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2647,7 +2647,7 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2683,7 +2683,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>9</v>
@@ -2721,7 +2721,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2765,7 +2765,7 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2780,7 +2780,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2801,7 +2801,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>6</v>
@@ -2816,7 +2816,7 @@
         <v>-1</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2842,7 +2842,7 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -2857,7 +2857,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2893,7 +2893,7 @@
         <v>-1</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2919,7 +2919,7 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -2934,7 +2934,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -2996,7 +2996,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3011,7 +3011,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3032,7 +3032,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -3073,7 +3073,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3088,7 +3088,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3109,7 +3109,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>9</v>
@@ -3150,7 +3150,7 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3165,7 +3165,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3186,7 +3186,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -3227,7 +3227,7 @@
         <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3242,7 +3242,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3263,7 +3263,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>5</v>
@@ -3278,7 +3278,7 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3304,7 +3304,7 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3340,7 +3340,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>7</v>
@@ -3372,7 +3372,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3384,7 +3384,7 @@
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3410,7 +3410,7 @@
         <v>9</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3446,7 +3446,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U37">
         <v>6</v>
@@ -3487,7 +3487,7 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -3502,7 +3502,7 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3564,7 +3564,7 @@
         <v>5</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -3679,7 +3679,7 @@
         <v>-1</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3720,7 +3720,7 @@
         <v>-1</v>
       </c>
       <c r="G42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L42">
         <v>-1</v>
@@ -3738,7 +3738,7 @@
         <v>-1</v>
       </c>
       <c r="Y42">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3902,22 +3902,22 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>80</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3963,19 +3963,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>97.06</v>
+        <v>94.12</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -3991,7 +3991,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4552,27 +4552,27 @@
         <v>136</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920129</v>
+        <v>20330051920131</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
         <v>60</v>
@@ -4592,7 +4592,7 @@
         <v>137</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
         <v>60</v>
@@ -4600,22 +4600,22 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920131</v>
+        <v>20330051920132</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4632,10 +4632,10 @@
         <v>138</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4652,10 +4652,10 @@
         <v>138</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4672,7 +4672,7 @@
         <v>138</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
         <v>60</v>
@@ -4680,19 +4680,19 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920132</v>
+        <v>20330051920133</v>
       </c>
       <c r="B35" t="s">
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s">
         <v>60</v>
@@ -4712,7 +4712,7 @@
         <v>139</v>
       </c>
       <c r="E36" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
         <v>60</v>
@@ -4720,19 +4720,19 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920133</v>
+        <v>20330051920134</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
         <v>60</v>
@@ -4752,7 +4752,7 @@
         <v>140</v>
       </c>
       <c r="E38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
         <v>60</v>
@@ -4760,19 +4760,19 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920134</v>
+        <v>20330051920135</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F39" t="s">
         <v>60</v>
@@ -4792,7 +4792,7 @@
         <v>133</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
         <v>60</v>
@@ -4800,36 +4800,36 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920135</v>
+        <v>20330051920136</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="D41" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920135</v>
+        <v>20330051920136</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="D42" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
@@ -4840,16 +4840,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920136</v>
+        <v>20330051920137</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
@@ -4860,39 +4860,39 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920136</v>
+        <v>20330051920137</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920136</v>
+        <v>19330051920383</v>
       </c>
       <c r="B45" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E45" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F45" t="s">
         <v>60</v>
@@ -4900,19 +4900,19 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920137</v>
+        <v>19330051920383</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F46" t="s">
         <v>60</v>
@@ -4920,16 +4920,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920137</v>
+        <v>20330051920139</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
@@ -4940,19 +4940,19 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>19330051920383</v>
+        <v>19330051920387</v>
       </c>
       <c r="B48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="D48" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F48" t="s">
         <v>60</v>
@@ -4960,19 +4960,19 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>19330051920383</v>
+        <v>20330051920140</v>
       </c>
       <c r="B49" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D49" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F49" t="s">
         <v>60</v>
@@ -4980,16 +4980,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>20330051920139</v>
+        <v>20330051920140</v>
       </c>
       <c r="B50" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
@@ -5000,19 +5000,19 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>19330051920387</v>
+        <v>20330051920141</v>
       </c>
       <c r="B51" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C51" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F51" t="s">
         <v>60</v>
@@ -5020,19 +5020,19 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>20330051920140</v>
+        <v>20330051920141</v>
       </c>
       <c r="B52" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C52" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F52" t="s">
         <v>60</v>
@@ -5040,19 +5040,19 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>20330051920140</v>
+        <v>20330051920389</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C53" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F53" t="s">
         <v>60</v>
@@ -5060,19 +5060,19 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>20330051920141</v>
+        <v>20330051920389</v>
       </c>
       <c r="B54" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E54" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F54" t="s">
         <v>60</v>
@@ -5080,19 +5080,19 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>20330051920141</v>
+        <v>20330051920144</v>
       </c>
       <c r="B55" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E55" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F55" t="s">
         <v>60</v>
@@ -5100,16 +5100,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>20330051920389</v>
+        <v>20330051920387</v>
       </c>
       <c r="B56" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C56" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D56" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E56" t="s">
         <v>7</v>
@@ -5120,16 +5120,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>20330051920389</v>
+        <v>20330051920387</v>
       </c>
       <c r="B57" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C57" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D57" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E57" t="s">
         <v>9</v>
@@ -5140,16 +5140,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>20330051920144</v>
+        <v>20330051920148</v>
       </c>
       <c r="B58" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C58" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D58" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E58" t="s">
         <v>7</v>
@@ -5160,19 +5160,19 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>20330051920387</v>
+        <v>20330051920148</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C59" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D59" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E59" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
         <v>60</v>
@@ -5180,56 +5180,56 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>20330051920387</v>
+        <v>20330051920151</v>
       </c>
       <c r="B60" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C60" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D60" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>20330051920148</v>
+        <v>20330051920151</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D61" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E61" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>20330051920148</v>
+        <v>20330051920151</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C62" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D62" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
@@ -5240,93 +5240,93 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>20330051920151</v>
+        <v>20330051920153</v>
       </c>
       <c r="B63" t="s">
-        <v>94</v>
-      </c>
-      <c r="C63" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="D63" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F63" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>20330051920151</v>
+        <v>20330051920153</v>
       </c>
       <c r="B64" t="s">
-        <v>94</v>
-      </c>
-      <c r="C64" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="D64" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E64" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>20330051920151</v>
+        <v>19330051920145</v>
       </c>
       <c r="B65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C65" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E65" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F65" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>20330051920153</v>
+        <v>19330051920145</v>
       </c>
       <c r="B66" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="C66" t="s">
+        <v>122</v>
       </c>
       <c r="D66" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E66" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F66" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>20330051920153</v>
+        <v>19330051920145</v>
       </c>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="C67" t="s">
+        <v>122</v>
       </c>
       <c r="D67" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E67" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F67" t="s">
         <v>60</v>
@@ -5346,109 +5346,29 @@
         <v>153</v>
       </c>
       <c r="E68" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>19330051920145</v>
+        <v>19330051920399</v>
       </c>
       <c r="B69" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C69" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D69" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E69" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F69" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920145</v>
-      </c>
-      <c r="B70" t="s">
-        <v>96</v>
-      </c>
-      <c r="C70" t="s">
-        <v>122</v>
-      </c>
-      <c r="D70" t="s">
-        <v>153</v>
-      </c>
-      <c r="E70" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>19330051920145</v>
-      </c>
-      <c r="B71" t="s">
-        <v>96</v>
-      </c>
-      <c r="C71" t="s">
-        <v>122</v>
-      </c>
-      <c r="D71" t="s">
-        <v>153</v>
-      </c>
-      <c r="E71" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>19330051920399</v>
-      </c>
-      <c r="B72" t="s">
-        <v>97</v>
-      </c>
-      <c r="C72" t="s">
-        <v>123</v>
-      </c>
-      <c r="D72" t="s">
-        <v>154</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>19330051920399</v>
-      </c>
-      <c r="B73" t="s">
-        <v>97</v>
-      </c>
-      <c r="C73" t="s">
-        <v>123</v>
-      </c>
-      <c r="D73" t="s">
-        <v>154</v>
-      </c>
-      <c r="E73" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5485,33 +5405,33 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920129</v>
+        <v>20330051920122</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920122</v>
+        <v>20330051920126</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -5519,16 +5439,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920126</v>
+        <v>20330051920129</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -5587,16 +5507,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920135</v>
+        <v>20330051920151</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -5604,50 +5524,50 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920136</v>
+        <v>20330051920124</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920151</v>
+        <v>20330051920125</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920124</v>
+        <v>20330051920127</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -5655,16 +5575,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920125</v>
+        <v>20330051920131</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -5672,16 +5592,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920127</v>
+        <v>20330051920133</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -5689,16 +5609,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920131</v>
+        <v>20330051920134</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -5706,16 +5626,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920133</v>
+        <v>20330051920135</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -5723,16 +5643,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920134</v>
+        <v>20330051920136</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -5873,33 +5793,33 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920399</v>
+        <v>18330051920393</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>18330051920393</v>
+        <v>19330051920360</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -5907,16 +5827,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920360</v>
+        <v>20330051920116</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -5924,16 +5844,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920116</v>
+        <v>20330051920121</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -5941,16 +5861,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920121</v>
+        <v>20330051920123</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -5958,16 +5878,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920123</v>
+        <v>20330051920128</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -5975,16 +5895,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920128</v>
+        <v>20330051920139</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -5992,16 +5912,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920139</v>
+        <v>19330051920387</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -6009,16 +5929,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920387</v>
+        <v>20330051920144</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -6026,16 +5946,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920144</v>
+        <v>19330051920399</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -6884,7 +6804,7 @@
         <v>62</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:7">

--- a/grupos/5ARHV - Estadisticos 20221.xlsx
+++ b/grupos/5ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="172">
   <si>
     <t>Materia</t>
   </si>
@@ -1110,13 +1110,13 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1152,7 +1152,7 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>-1</v>
@@ -1187,13 +1187,13 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1223,13 +1223,13 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>7</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1264,13 +1264,13 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1300,7 +1300,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1341,13 +1341,13 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1418,13 +1418,13 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1454,13 +1454,13 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1495,7 +1495,7 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1531,7 +1531,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1649,13 +1649,13 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1726,13 +1726,13 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1762,13 +1762,13 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>-1</v>
@@ -1803,13 +1803,13 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1957,13 +1957,13 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -1999,7 +1999,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>-1</v>
@@ -2034,13 +2034,13 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2076,7 +2076,7 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>-1</v>
@@ -2188,13 +2188,13 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2224,7 +2224,7 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2342,13 +2342,13 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2419,7 +2419,7 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2496,7 +2496,7 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2573,13 +2573,13 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2650,13 +2650,13 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2692,7 +2692,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>-1</v>
@@ -2768,13 +2768,13 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2845,13 +2845,13 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2881,13 +2881,13 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>-1</v>
@@ -2922,13 +2922,13 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -2958,7 +2958,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -2999,13 +2999,13 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3035,13 +3035,13 @@
         <v>9</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>-1</v>
@@ -3076,13 +3076,13 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3153,13 +3153,13 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3230,13 +3230,13 @@
         <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3266,7 +3266,7 @@
         <v>9</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3313,7 +3313,7 @@
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3349,7 +3349,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>-1</v>
@@ -3413,7 +3413,7 @@
         <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -3449,7 +3449,7 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V37">
         <v>-1</v>
@@ -3490,13 +3490,13 @@
         <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
         <v>-1</v>
@@ -3867,19 +3867,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>50</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G4">
-        <v>32.35</v>
+        <v>14.71</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>6</v>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -6087,7 +6087,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6257,16 +6257,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920125</v>
+        <v>20330051920124</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -6280,16 +6280,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920125</v>
+        <v>20330051920124</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -6303,16 +6303,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920127</v>
+        <v>20330051920125</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
         <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -6326,16 +6326,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920127</v>
+        <v>20330051920125</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
         <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -6349,16 +6349,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920131</v>
+        <v>20330051920127</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -6372,16 +6372,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920131</v>
+        <v>20330051920127</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -6395,16 +6395,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920134</v>
+        <v>20330051920131</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -6418,16 +6418,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920134</v>
+        <v>20330051920131</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -6441,16 +6441,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920137</v>
+        <v>20330051920134</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -6464,16 +6464,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920137</v>
+        <v>20330051920134</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -6487,16 +6487,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920383</v>
+        <v>20330051920137</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -6510,16 +6510,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920383</v>
+        <v>20330051920137</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -6533,16 +6533,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920141</v>
+        <v>19330051920383</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -6556,16 +6556,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920141</v>
+        <v>19330051920383</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -6579,16 +6579,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920389</v>
+        <v>20330051920140</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -6602,16 +6602,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920389</v>
+        <v>20330051920140</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -6625,42 +6625,42 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920144</v>
+        <v>20330051920141</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920144</v>
+        <v>20330051920141</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
         <v>60</v>
@@ -6671,16 +6671,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920387</v>
+        <v>20330051920389</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -6694,16 +6694,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920387</v>
+        <v>20330051920389</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -6717,16 +6717,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920148</v>
+        <v>20330051920387</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
@@ -6740,16 +6740,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920148</v>
+        <v>20330051920387</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -6763,19 +6763,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330051920399</v>
+        <v>20330051920148</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
         <v>60</v>
@@ -6786,39 +6786,36 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>19330051920399</v>
+        <v>20330051920148</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>18330051920393</v>
+        <v>20330051920153</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
@@ -6832,19 +6829,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920121</v>
+        <v>20330051920153</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
         <v>60</v>
@@ -6855,16 +6849,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920128</v>
+        <v>19330051920399</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -6878,42 +6872,42 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920139</v>
+        <v>19330051920399</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051920387</v>
+        <v>18330051920393</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F36" t="s">
         <v>60</v>
@@ -6924,25 +6918,117 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920143</v>
+        <v>20330051920121</v>
       </c>
       <c r="B37" t="s">
-        <v>158</v>
+        <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="E37" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>20330051920128</v>
+      </c>
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>60</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>20330051920139</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>19330051920387</v>
+      </c>
+      <c r="B40" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" t="s">
+        <v>145</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>60</v>
+      </c>
+      <c r="G40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>20330051920144</v>
+      </c>
+      <c r="B41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" t="s">
+        <v>149</v>
+      </c>
+      <c r="E41" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ARHV - Estadisticos 20221.xlsx
+++ b/grupos/5ARHV - Estadisticos 20221.xlsx
@@ -1122,7 +1122,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1158,7 +1158,7 @@
         <v>-1</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1892,7 +1892,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1928,7 +1928,7 @@
         <v>-1</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1969,7 +1969,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2005,7 +2005,7 @@
         <v>-1</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2277,7 +2277,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2313,7 +2313,7 @@
         <v>-1</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2508,7 +2508,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2662,7 +2662,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2698,7 +2698,7 @@
         <v>-1</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -3319,7 +3319,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3355,7 +3355,7 @@
         <v>-1</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3425,7 +3425,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3461,7 +3461,7 @@
         <v>-1</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3579,7 +3579,7 @@
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3632,7 +3632,7 @@
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -3644,7 +3644,7 @@
         <v>8</v>
       </c>
       <c r="Y40">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3726,7 +3726,7 @@
         <v>-1</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -3911,7 +3911,7 @@
         <v>20</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/5ARHV - Estadisticos 20221.xlsx
+++ b/grupos/5ARHV - Estadisticos 20221.xlsx
@@ -1031,7 +1031,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -1049,7 +1049,7 @@
         <v>-1</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -1113,7 +1113,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -1149,7 +1149,7 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1190,13 +1190,13 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -1226,13 +1226,13 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1267,13 +1267,13 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1303,13 +1303,13 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1350,7 +1350,7 @@
         <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1386,7 +1386,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1427,7 +1427,7 @@
         <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>9</v>
@@ -1463,7 +1463,7 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1652,7 +1652,7 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -1688,7 +1688,7 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -2037,7 +2037,7 @@
         <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -2073,7 +2073,7 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2771,7 +2771,7 @@
         <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>10</v>
@@ -2807,7 +2807,7 @@
         <v>6</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2925,7 +2925,7 @@
         <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
         <v>10</v>
@@ -3156,13 +3156,13 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3233,13 +3233,13 @@
         <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>10</v>
@@ -3269,13 +3269,13 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>10</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3369,7 +3369,7 @@
         <v>8</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>6</v>
@@ -3381,7 +3381,7 @@
         <v>-1</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -3493,13 +3493,13 @@
         <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
         <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
         <v>9</v>
@@ -3529,13 +3529,13 @@
         <v>9</v>
       </c>
       <c r="V38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W38">
         <v>10</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>10</v>
@@ -3570,7 +3570,7 @@
         <v>-1</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
         <v>-1</v>
@@ -3606,7 +3606,7 @@
         <v>-1</v>
       </c>
       <c r="V39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W39">
         <v>-1</v>
@@ -3629,7 +3629,7 @@
         <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
         <v>5</v>
@@ -3641,7 +3641,7 @@
         <v>-1</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y40">
         <v>7</v>
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I2">
         <v>30</v>
@@ -3835,19 +3835,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>30.56</v>
+        <v>27.78</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>25</v>

--- a/grupos/5ARHV - Estadisticos 20221.xlsx
+++ b/grupos/5ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="172">
   <si>
     <t>Materia</t>
   </si>
@@ -200,12 +200,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
@@ -227,15 +227,30 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>JARED JESUS</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
     <t>BRETON</t>
   </si>
   <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>CONGUILLO</t>
+  </si>
+  <si>
     <t>CUATRA</t>
   </si>
   <si>
@@ -293,6 +308,12 @@
     <t>PACHECO</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>DE LA ROSA</t>
   </si>
   <si>
@@ -302,13 +323,16 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
+    <t>VERA</t>
   </si>
   <si>
     <t>ZARATE</t>
@@ -374,19 +398,28 @@
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
     <t>SALAZAR</t>
   </si>
   <si>
+    <t>QUIAHUA</t>
+  </si>
+  <si>
     <t>RAMON</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>ESPINOSA</t>
+    <t>PAZOS</t>
   </si>
   <si>
     <t>VERGEL</t>
@@ -398,9 +431,15 @@
     <t>AMYRA NAHOMY</t>
   </si>
   <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
     <t>AMARANTA DENISSE</t>
   </si>
   <si>
+    <t>CONSUELO DALILA</t>
+  </si>
+  <si>
     <t>MARIA</t>
   </si>
   <si>
@@ -467,73 +506,34 @@
     <t>TAILY</t>
   </si>
   <si>
+    <t>INGRID YALITH</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
     <t>ALONDRA</t>
   </si>
   <si>
+    <t>LORENA</t>
+  </si>
+  <si>
     <t>MEILYN ADABEL</t>
   </si>
   <si>
+    <t>DIANA VIANNEY</t>
+  </si>
+  <si>
     <t>CONSTANZA XIMENA</t>
   </si>
   <si>
     <t>KIMBERLY</t>
   </si>
   <si>
-    <t>JARED JESUS</t>
+    <t>CARLA DANIELA</t>
   </si>
   <si>
     <t>PAULINA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PAZOS</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>INGRID YALITH</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>DIANA VIANNEY</t>
-  </si>
-  <si>
-    <t>CARLA DANIELA</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1019,7 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>9</v>
@@ -1028,7 +1028,7 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -1046,7 +1046,7 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1060,13 +1060,13 @@
         <v>13</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -1078,7 +1078,7 @@
         <v>-1</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1101,7 +1101,7 @@
         <v>8</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1119,7 +1119,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -1155,7 +1155,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1326,7 +1326,7 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -1344,7 +1344,7 @@
         <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>9</v>
@@ -1380,7 +1380,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1403,7 +1403,7 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -1421,7 +1421,7 @@
         <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>10</v>
@@ -1457,7 +1457,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1480,13 +1480,13 @@
         <v>5</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>7</v>
@@ -1498,13 +1498,13 @@
         <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>7</v>
@@ -1534,13 +1534,13 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1554,16 +1554,16 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -1572,16 +1572,16 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -1608,16 +1608,16 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1640,7 +1640,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>9</v>
@@ -1658,7 +1658,7 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>9</v>
@@ -1694,7 +1694,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1711,13 +1711,13 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>8</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>9</v>
@@ -1729,13 +1729,13 @@
         <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>7</v>
@@ -1765,13 +1765,13 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>9</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1788,13 +1788,13 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E15">
         <v>10</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>9</v>
@@ -1806,13 +1806,13 @@
         <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>9</v>
@@ -1842,13 +1842,13 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>10</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1862,16 +1862,16 @@
         <v>8</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>7</v>
@@ -1880,16 +1880,16 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -1916,16 +1916,16 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -1942,13 +1942,13 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>7</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -1960,13 +1960,13 @@
         <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>4</v>
@@ -1996,13 +1996,13 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2025,7 +2025,7 @@
         <v>9</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>9</v>
@@ -2043,7 +2043,7 @@
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -2093,16 +2093,16 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2111,16 +2111,16 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -2147,16 +2147,16 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2173,13 +2173,13 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E20">
         <v>10</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>9</v>
@@ -2191,13 +2191,13 @@
         <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>8</v>
@@ -2227,13 +2227,13 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2247,16 +2247,16 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G21">
         <v>7</v>
@@ -2265,16 +2265,16 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>5</v>
@@ -2301,16 +2301,16 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2327,13 +2327,13 @@
         <v>5</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E22">
         <v>9</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G22">
         <v>8</v>
@@ -2345,13 +2345,13 @@
         <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>9</v>
@@ -2381,13 +2381,13 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2404,13 +2404,13 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>8</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2422,13 +2422,13 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2458,13 +2458,13 @@
         <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2481,13 +2481,13 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>8</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -2499,13 +2499,13 @@
         <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2535,13 +2535,13 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2558,13 +2558,13 @@
         <v>6</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>10</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>8</v>
@@ -2576,13 +2576,13 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -2612,13 +2612,13 @@
         <v>6</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>10</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2635,13 +2635,13 @@
         <v>9</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E26">
         <v>7</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>8</v>
@@ -2653,13 +2653,13 @@
         <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>4</v>
@@ -2689,13 +2689,13 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2706,19 +2706,19 @@
         <v>35</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G27">
         <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>6</v>
@@ -2733,10 +2733,10 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2759,7 +2759,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>9</v>
@@ -2777,7 +2777,7 @@
         <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>10</v>
@@ -2813,7 +2813,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2830,13 +2830,13 @@
         <v>5</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E29">
         <v>8</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>9</v>
@@ -2848,13 +2848,13 @@
         <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>7</v>
@@ -2884,13 +2884,13 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>9</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -2913,7 +2913,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>9</v>
@@ -2931,7 +2931,7 @@
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>9</v>
@@ -2967,7 +2967,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -2984,13 +2984,13 @@
         <v>6</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E31">
         <v>8</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>9</v>
@@ -3002,13 +3002,13 @@
         <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>9</v>
@@ -3038,13 +3038,13 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>9</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -3061,13 +3061,13 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>10</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -3079,13 +3079,13 @@
         <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>9</v>
@@ -3115,13 +3115,13 @@
         <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>10</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3292,13 +3292,13 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E35">
         <v>8</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G35">
         <v>8</v>
@@ -3307,16 +3307,16 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>4</v>
@@ -3343,16 +3343,16 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>9</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -3398,13 +3398,13 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E37">
         <v>9</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G37">
         <v>9</v>
@@ -3416,13 +3416,13 @@
         <v>7</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>7</v>
@@ -3452,13 +3452,13 @@
         <v>7</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>9</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y37">
         <v>8</v>
@@ -3549,16 +3549,16 @@
         <v>7</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>6</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -3567,16 +3567,16 @@
         <v>6</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
         <v>5</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
         <v>5</v>
@@ -3603,16 +3603,16 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V39">
         <v>5</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -3655,13 +3655,13 @@
         <v>-1</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -3670,13 +3670,13 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>5</v>
@@ -3700,13 +3700,13 @@
         <v>-1</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y41">
         <v>5</v>
@@ -3717,13 +3717,13 @@
         <v>50</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G42">
         <v>5</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M42">
         <v>5</v>
@@ -3735,7 +3735,7 @@
         <v>-1</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y42">
         <v>5</v>
@@ -3794,98 +3794,98 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
       </c>
       <c r="C2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>32.35</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>27.78</v>
+        <v>77.5</v>
       </c>
       <c r="G3">
-        <v>2.78</v>
+        <v>22.5</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>69.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>67.65000000000001</v>
+        <v>77.78</v>
       </c>
       <c r="G4">
-        <v>14.71</v>
+        <v>22.22</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3931,25 +3931,25 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>81.81999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>12.12</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3991,7 +3991,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4020,1356 +4020,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>18330051920393</v>
+        <v>19330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920360</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920116</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920121</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920427</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920427</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920427</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920122</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920122</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920122</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920122</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920123</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" t="s">
-        <v>130</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920124</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920124</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920125</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" t="s">
-        <v>132</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920125</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>132</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920126</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>133</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920126</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" t="s">
-        <v>133</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920126</v>
-      </c>
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920126</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920127</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920127</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920128</v>
-      </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920129</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920129</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920129</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" t="s">
-        <v>136</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920129</v>
-      </c>
-      <c r="B28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920131</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920131</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920132</v>
-      </c>
-      <c r="B31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" t="s">
-        <v>138</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920132</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>109</v>
-      </c>
-      <c r="D32" t="s">
-        <v>138</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920132</v>
-      </c>
-      <c r="B33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>109</v>
-      </c>
-      <c r="D33" t="s">
-        <v>138</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920132</v>
-      </c>
-      <c r="B34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920133</v>
-      </c>
-      <c r="B35" t="s">
-        <v>80</v>
-      </c>
-      <c r="C35" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920133</v>
-      </c>
-      <c r="B36" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" t="s">
-        <v>110</v>
-      </c>
-      <c r="D36" t="s">
-        <v>139</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920134</v>
-      </c>
-      <c r="B37" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" t="s">
-        <v>111</v>
-      </c>
-      <c r="D37" t="s">
-        <v>140</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920134</v>
-      </c>
-      <c r="B38" t="s">
-        <v>81</v>
-      </c>
-      <c r="C38" t="s">
-        <v>111</v>
-      </c>
-      <c r="D38" t="s">
-        <v>140</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920135</v>
-      </c>
-      <c r="B39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" t="s">
-        <v>112</v>
-      </c>
-      <c r="D39" t="s">
-        <v>133</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920135</v>
-      </c>
-      <c r="B40" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" t="s">
-        <v>112</v>
-      </c>
-      <c r="D40" t="s">
-        <v>133</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920136</v>
-      </c>
-      <c r="B41" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" t="s">
-        <v>141</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920136</v>
-      </c>
-      <c r="B42" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" t="s">
-        <v>141</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920137</v>
-      </c>
-      <c r="B43" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" t="s">
-        <v>113</v>
-      </c>
-      <c r="D43" t="s">
-        <v>142</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920137</v>
-      </c>
-      <c r="B44" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" t="s">
-        <v>113</v>
-      </c>
-      <c r="D44" t="s">
-        <v>142</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920383</v>
-      </c>
-      <c r="B45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" t="s">
-        <v>114</v>
-      </c>
-      <c r="D45" t="s">
-        <v>143</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920383</v>
-      </c>
-      <c r="B46" t="s">
-        <v>85</v>
-      </c>
-      <c r="C46" t="s">
-        <v>114</v>
-      </c>
-      <c r="D46" t="s">
-        <v>143</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920139</v>
-      </c>
-      <c r="B47" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" t="s">
-        <v>115</v>
-      </c>
-      <c r="D47" t="s">
-        <v>144</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920387</v>
-      </c>
-      <c r="B48" t="s">
-        <v>87</v>
-      </c>
-      <c r="C48" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" t="s">
-        <v>145</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920140</v>
-      </c>
-      <c r="B49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" t="s">
-        <v>112</v>
-      </c>
-      <c r="D49" t="s">
-        <v>146</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920140</v>
-      </c>
-      <c r="B50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C50" t="s">
-        <v>112</v>
-      </c>
-      <c r="D50" t="s">
-        <v>146</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920141</v>
-      </c>
-      <c r="B51" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" t="s">
-        <v>116</v>
-      </c>
-      <c r="D51" t="s">
-        <v>147</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920141</v>
-      </c>
-      <c r="B52" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" t="s">
-        <v>116</v>
-      </c>
-      <c r="D52" t="s">
-        <v>147</v>
-      </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920389</v>
-      </c>
-      <c r="B53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" t="s">
-        <v>117</v>
-      </c>
-      <c r="D53" t="s">
-        <v>148</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920389</v>
-      </c>
-      <c r="B54" t="s">
-        <v>90</v>
-      </c>
-      <c r="C54" t="s">
-        <v>117</v>
-      </c>
-      <c r="D54" t="s">
-        <v>148</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920144</v>
-      </c>
-      <c r="B55" t="s">
-        <v>91</v>
-      </c>
-      <c r="C55" t="s">
-        <v>118</v>
-      </c>
-      <c r="D55" t="s">
-        <v>149</v>
-      </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920387</v>
-      </c>
-      <c r="B56" t="s">
-        <v>92</v>
-      </c>
-      <c r="C56" t="s">
-        <v>119</v>
-      </c>
-      <c r="D56" t="s">
-        <v>146</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920387</v>
-      </c>
-      <c r="B57" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" t="s">
-        <v>119</v>
-      </c>
-      <c r="D57" t="s">
-        <v>146</v>
-      </c>
-      <c r="E57" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920148</v>
-      </c>
-      <c r="B58" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" t="s">
-        <v>120</v>
-      </c>
-      <c r="D58" t="s">
-        <v>150</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>20330051920148</v>
-      </c>
-      <c r="B59" t="s">
-        <v>93</v>
-      </c>
-      <c r="C59" t="s">
-        <v>120</v>
-      </c>
-      <c r="D59" t="s">
-        <v>150</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920151</v>
-      </c>
-      <c r="B60" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" t="s">
-        <v>121</v>
-      </c>
-      <c r="D60" t="s">
-        <v>151</v>
-      </c>
-      <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920151</v>
-      </c>
-      <c r="B61" t="s">
-        <v>94</v>
-      </c>
-      <c r="C61" t="s">
-        <v>121</v>
-      </c>
-      <c r="D61" t="s">
-        <v>151</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920151</v>
-      </c>
-      <c r="B62" t="s">
-        <v>94</v>
-      </c>
-      <c r="C62" t="s">
-        <v>121</v>
-      </c>
-      <c r="D62" t="s">
-        <v>151</v>
-      </c>
-      <c r="E62" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920153</v>
-      </c>
-      <c r="B63" t="s">
-        <v>95</v>
-      </c>
-      <c r="D63" t="s">
-        <v>152</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920153</v>
-      </c>
-      <c r="B64" t="s">
-        <v>95</v>
-      </c>
-      <c r="D64" t="s">
-        <v>152</v>
-      </c>
-      <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920145</v>
-      </c>
-      <c r="B65" t="s">
-        <v>96</v>
-      </c>
-      <c r="C65" t="s">
-        <v>122</v>
-      </c>
-      <c r="D65" t="s">
-        <v>153</v>
-      </c>
-      <c r="E65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F65" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920145</v>
-      </c>
-      <c r="B66" t="s">
-        <v>96</v>
-      </c>
-      <c r="C66" t="s">
-        <v>122</v>
-      </c>
-      <c r="D66" t="s">
-        <v>153</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920145</v>
-      </c>
-      <c r="B67" t="s">
-        <v>96</v>
-      </c>
-      <c r="C67" t="s">
-        <v>122</v>
-      </c>
-      <c r="D67" t="s">
-        <v>153</v>
-      </c>
-      <c r="E67" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920145</v>
-      </c>
-      <c r="B68" t="s">
-        <v>96</v>
-      </c>
-      <c r="C68" t="s">
-        <v>122</v>
-      </c>
-      <c r="D68" t="s">
-        <v>153</v>
-      </c>
-      <c r="E68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920399</v>
-      </c>
-      <c r="B69" t="s">
-        <v>97</v>
-      </c>
-      <c r="C69" t="s">
-        <v>123</v>
-      </c>
-      <c r="D69" t="s">
-        <v>154</v>
-      </c>
-      <c r="E69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -5405,44 +4071,44 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920122</v>
+        <v>19330051920145</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920126</v>
+        <v>18330051920393</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920129</v>
+        <v>19330051920360</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
         <v>107</v>
@@ -5451,480 +4117,483 @@
         <v>136</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920132</v>
+        <v>20330051920115</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920145</v>
+        <v>20330051920116</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920427</v>
+        <v>20330051920118</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920151</v>
+        <v>20330051920121</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920124</v>
+        <v>19330051920427</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920125</v>
+        <v>20330051920122</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920127</v>
+        <v>20330051920123</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920131</v>
+        <v>20330051920124</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920133</v>
+        <v>20330051920125</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920134</v>
+        <v>20330051920126</v>
       </c>
       <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
         <v>81</v>
       </c>
-      <c r="C14" t="s">
-        <v>111</v>
-      </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920135</v>
+        <v>20330051920127</v>
       </c>
       <c r="B15" t="s">
         <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920136</v>
+        <v>20330051920128</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920137</v>
+        <v>20330051920129</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920383</v>
+        <v>20330051920131</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920140</v>
+        <v>20330051920132</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920141</v>
+        <v>20330051920133</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920389</v>
+        <v>20330051920134</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920387</v>
+        <v>20330051920135</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
         <v>146</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920148</v>
+        <v>20330051920136</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920153</v>
+        <v>20330051920137</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>18330051920393</v>
+        <v>19330051920383</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920360</v>
+        <v>20330051920139</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920116</v>
+        <v>19330051920387</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920121</v>
+        <v>20330051920140</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920123</v>
+        <v>20330051920141</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920128</v>
+        <v>20330051920389</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920139</v>
+        <v>20330051920142</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920387</v>
+        <v>20330051920143</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5932,44 +4601,44 @@
         <v>20330051920144</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920399</v>
+        <v>20330051920387</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920115</v>
+        <v>18330051920185</v>
       </c>
       <c r="B35" t="s">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="D35" t="s">
         <v>165</v>
@@ -5980,13 +4649,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920118</v>
+        <v>20330051920148</v>
       </c>
       <c r="B36" t="s">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="D36" t="s">
         <v>166</v>
@@ -5997,13 +4666,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>20330051920142</v>
+        <v>20330051920150</v>
       </c>
       <c r="B37" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="D37" t="s">
         <v>167</v>
@@ -6014,13 +4683,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>20330051920143</v>
+        <v>20330051920151</v>
       </c>
       <c r="B38" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
         <v>168</v>
@@ -6031,13 +4700,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>18330051920185</v>
+        <v>20330051920153</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="D39" t="s">
         <v>169</v>
@@ -6048,13 +4714,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>20330051920150</v>
+        <v>18330051920189</v>
       </c>
       <c r="B40" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="D40" t="s">
         <v>170</v>
@@ -6065,13 +4731,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>18330051920189</v>
+        <v>19330051920399</v>
       </c>
       <c r="B41" t="s">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="D41" t="s">
         <v>171</v>
@@ -6087,7 +4753,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6122,22 +4788,22 @@
         <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -6145,13 +4811,13 @@
         <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6168,19 +4834,19 @@
         <v>20330051920116</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6188,45 +4854,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920116</v>
+        <v>20330051920123</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
         <v>60</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920123</v>
+        <v>20330051920133</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6234,801 +4900,25 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920123</v>
+        <v>19330051920399</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920124</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920124</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920125</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920125</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920127</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920127</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920131</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" t="s">
-        <v>137</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920131</v>
-      </c>
-      <c r="B15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920134</v>
-      </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920134</v>
-      </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" t="s">
-        <v>140</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920137</v>
-      </c>
-      <c r="B18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" t="s">
-        <v>142</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920137</v>
-      </c>
-      <c r="B19" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" t="s">
-        <v>142</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920383</v>
-      </c>
-      <c r="B20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" t="s">
-        <v>114</v>
-      </c>
-      <c r="D20" t="s">
-        <v>143</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920383</v>
-      </c>
-      <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920140</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" t="s">
-        <v>146</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920140</v>
-      </c>
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" t="s">
-        <v>146</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920141</v>
-      </c>
-      <c r="B24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" t="s">
-        <v>147</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920141</v>
-      </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" t="s">
-        <v>116</v>
-      </c>
-      <c r="D25" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920389</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" t="s">
-        <v>148</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920389</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" t="s">
-        <v>148</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920387</v>
-      </c>
-      <c r="B28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D28" t="s">
-        <v>146</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920387</v>
-      </c>
-      <c r="B29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" t="s">
-        <v>146</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920148</v>
-      </c>
-      <c r="B30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" t="s">
-        <v>150</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920148</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920153</v>
-      </c>
-      <c r="B32" t="s">
-        <v>95</v>
-      </c>
-      <c r="D32" t="s">
-        <v>152</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>60</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920153</v>
-      </c>
-      <c r="B33" t="s">
-        <v>95</v>
-      </c>
-      <c r="D33" t="s">
-        <v>152</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>19330051920399</v>
-      </c>
-      <c r="B34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" t="s">
-        <v>154</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>19330051920399</v>
-      </c>
-      <c r="B35" t="s">
-        <v>97</v>
-      </c>
-      <c r="C35" t="s">
-        <v>123</v>
-      </c>
-      <c r="D35" t="s">
-        <v>154</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>62</v>
-      </c>
-      <c r="G35">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>18330051920393</v>
-      </c>
-      <c r="B36" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" t="s">
-        <v>124</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>60</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>20330051920121</v>
-      </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" t="s">
-        <v>101</v>
-      </c>
-      <c r="D37" t="s">
-        <v>127</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>60</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>20330051920128</v>
-      </c>
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" t="s">
-        <v>106</v>
-      </c>
-      <c r="D38" t="s">
-        <v>135</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>20330051920139</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" t="s">
-        <v>115</v>
-      </c>
-      <c r="D39" t="s">
-        <v>144</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>19330051920387</v>
-      </c>
-      <c r="B40" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" t="s">
-        <v>75</v>
-      </c>
-      <c r="D40" t="s">
-        <v>145</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>60</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>20330051920144</v>
-      </c>
-      <c r="B41" t="s">
-        <v>91</v>
-      </c>
-      <c r="C41" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" t="s">
-        <v>149</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ARHV - Estadisticos 20221.xlsx
+++ b/grupos/5ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="179">
   <si>
     <t>Materia</t>
   </si>
@@ -143,12 +143,18 @@
     <t>PACHECO MAZAHUA TAILY</t>
   </si>
   <si>
+    <t>RAMOS PEREZ ASTRID</t>
+  </si>
+  <si>
     <t>RIVERA ROMERO INGRID YALITH</t>
   </si>
   <si>
     <t>RODRIGUEZ BARRAGAN LUCERO</t>
   </si>
   <si>
+    <t>ROJAS DE LA CRUZ ITZEL ISABEL</t>
+  </si>
+  <si>
     <t>ROSAS SALAZAR MARIA FERNANDA</t>
   </si>
   <si>
@@ -227,12 +233,30 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>ESPINOSA</t>
   </si>
   <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>ITZEL ISABEL</t>
+  </si>
+  <si>
     <t>JARED JESUS</t>
   </si>
   <si>
@@ -414,9 +438,6 @@
   </si>
   <si>
     <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
   </si>
   <si>
     <t>PAZOS</t>
@@ -891,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3131,52 +3152,16 @@
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B33">
-        <v>9</v>
-      </c>
-      <c r="C33">
-        <v>10</v>
-      </c>
-      <c r="D33">
-        <v>10</v>
-      </c>
-      <c r="E33">
-        <v>10</v>
-      </c>
       <c r="F33">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="G33">
-        <v>10</v>
-      </c>
-      <c r="H33">
-        <v>10</v>
-      </c>
-      <c r="I33">
-        <v>10</v>
-      </c>
-      <c r="J33">
-        <v>10</v>
-      </c>
-      <c r="K33">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="L33">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="M33">
-        <v>10</v>
-      </c>
-      <c r="N33">
-        <v>-1</v>
-      </c>
-      <c r="O33">
-        <v>-1</v>
-      </c>
-      <c r="P33">
-        <v>-1</v>
-      </c>
-      <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
@@ -3185,23 +3170,11 @@
       <c r="S33">
         <v>-1</v>
       </c>
-      <c r="T33">
-        <v>10</v>
-      </c>
-      <c r="U33">
-        <v>10</v>
-      </c>
-      <c r="V33">
-        <v>10</v>
-      </c>
-      <c r="W33">
-        <v>10</v>
-      </c>
       <c r="X33">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3209,28 +3182,28 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E34">
         <v>10</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H34">
         <v>10</v>
       </c>
       <c r="I34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J34">
         <v>10</v>
@@ -3239,7 +3212,7 @@
         <v>10</v>
       </c>
       <c r="L34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>10</v>
@@ -3263,19 +3236,19 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>10</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3286,40 +3259,40 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H35">
         <v>10</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3340,22 +3313,22 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3363,16 +3336,16 @@
         <v>44</v>
       </c>
       <c r="F36">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="G36">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="L36">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="M36">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3381,10 +3354,10 @@
         <v>-1</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3395,37 +3368,37 @@
         <v>9</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F37">
         <v>10</v>
       </c>
       <c r="G37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H37">
         <v>10</v>
       </c>
       <c r="I37">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>10</v>
       </c>
       <c r="M37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3449,10 +3422,10 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>9</v>
@@ -3461,60 +3434,24 @@
         <v>10</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>10</v>
-      </c>
-      <c r="C38">
-        <v>9</v>
-      </c>
-      <c r="D38">
-        <v>9</v>
-      </c>
-      <c r="E38">
-        <v>10</v>
-      </c>
       <c r="F38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G38">
-        <v>10</v>
-      </c>
-      <c r="H38">
-        <v>10</v>
-      </c>
-      <c r="I38">
-        <v>9</v>
-      </c>
-      <c r="J38">
-        <v>10</v>
-      </c>
-      <c r="K38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L38">
         <v>10</v>
       </c>
       <c r="M38">
-        <v>9</v>
-      </c>
-      <c r="N38">
-        <v>-1</v>
-      </c>
-      <c r="O38">
-        <v>-1</v>
-      </c>
-      <c r="P38">
-        <v>-1</v>
-      </c>
-      <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3522,23 +3459,11 @@
       <c r="S38">
         <v>-1</v>
       </c>
-      <c r="T38">
-        <v>10</v>
-      </c>
-      <c r="U38">
-        <v>9</v>
-      </c>
-      <c r="V38">
-        <v>10</v>
-      </c>
-      <c r="W38">
-        <v>10</v>
-      </c>
       <c r="X38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y38">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3546,40 +3471,40 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G39">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3600,39 +3525,75 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W39">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="B40">
+        <v>10</v>
+      </c>
+      <c r="C40">
+        <v>9</v>
+      </c>
+      <c r="D40">
+        <v>9</v>
+      </c>
+      <c r="E40">
+        <v>10</v>
+      </c>
       <c r="F40">
         <v>8</v>
       </c>
       <c r="G40">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="H40">
+        <v>10</v>
+      </c>
+      <c r="I40">
+        <v>9</v>
+      </c>
+      <c r="J40">
+        <v>10</v>
+      </c>
+      <c r="K40">
+        <v>10</v>
       </c>
       <c r="L40">
         <v>10</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="N40">
+        <v>-1</v>
+      </c>
+      <c r="O40">
+        <v>-1</v>
+      </c>
+      <c r="P40">
+        <v>-1</v>
+      </c>
+      <c r="Q40">
+        <v>-1</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -3640,11 +3601,23 @@
       <c r="S40">
         <v>-1</v>
       </c>
+      <c r="T40">
+        <v>10</v>
+      </c>
+      <c r="U40">
+        <v>9</v>
+      </c>
+      <c r="V40">
+        <v>10</v>
+      </c>
+      <c r="W40">
+        <v>10</v>
+      </c>
       <c r="X40">
         <v>9</v>
       </c>
       <c r="Y40">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3652,12 +3625,15 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C41">
         <v>5</v>
       </c>
       <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41">
         <v>5</v>
       </c>
       <c r="F41">
@@ -3667,7 +3643,7 @@
         <v>5</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>5</v>
@@ -3675,6 +3651,9 @@
       <c r="J41">
         <v>5</v>
       </c>
+      <c r="K41">
+        <v>5</v>
+      </c>
       <c r="L41">
         <v>5</v>
       </c>
@@ -3690,6 +3669,9 @@
       <c r="P41">
         <v>-1</v>
       </c>
+      <c r="Q41">
+        <v>-1</v>
+      </c>
       <c r="R41">
         <v>-1</v>
       </c>
@@ -3697,12 +3679,15 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U41">
         <v>5</v>
       </c>
       <c r="V41">
+        <v>5</v>
+      </c>
+      <c r="W41">
         <v>5</v>
       </c>
       <c r="X41">
@@ -3717,13 +3702,13 @@
         <v>50</v>
       </c>
       <c r="F42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M42">
         <v>5</v>
@@ -3735,9 +3720,103 @@
         <v>-1</v>
       </c>
       <c r="X42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y42">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25">
+      <c r="A43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43">
+        <v>-1</v>
+      </c>
+      <c r="C43">
+        <v>5</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43">
+        <v>5</v>
+      </c>
+      <c r="H43">
+        <v>-1</v>
+      </c>
+      <c r="I43">
+        <v>5</v>
+      </c>
+      <c r="J43">
+        <v>5</v>
+      </c>
+      <c r="L43">
+        <v>5</v>
+      </c>
+      <c r="M43">
+        <v>5</v>
+      </c>
+      <c r="N43">
+        <v>-1</v>
+      </c>
+      <c r="O43">
+        <v>-1</v>
+      </c>
+      <c r="P43">
+        <v>-1</v>
+      </c>
+      <c r="R43">
+        <v>-1</v>
+      </c>
+      <c r="S43">
+        <v>-1</v>
+      </c>
+      <c r="T43">
+        <v>-1</v>
+      </c>
+      <c r="U43">
+        <v>5</v>
+      </c>
+      <c r="V43">
+        <v>5</v>
+      </c>
+      <c r="X43">
+        <v>5</v>
+      </c>
+      <c r="Y43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44">
+        <v>7</v>
+      </c>
+      <c r="G44">
+        <v>5</v>
+      </c>
+      <c r="L44">
+        <v>7</v>
+      </c>
+      <c r="M44">
+        <v>5</v>
+      </c>
+      <c r="R44">
+        <v>-1</v>
+      </c>
+      <c r="S44">
+        <v>-1</v>
+      </c>
+      <c r="X44">
+        <v>7</v>
+      </c>
+      <c r="Y44">
         <v>5</v>
       </c>
     </row>
@@ -3765,31 +3844,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3797,7 +3876,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2">
         <v>34</v>
@@ -3829,10 +3908,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D3">
         <v>31</v>
@@ -3841,77 +3920,77 @@
         <v>9</v>
       </c>
       <c r="F3">
-        <v>77.5</v>
+        <v>73.81</v>
       </c>
       <c r="G3">
-        <v>22.5</v>
+        <v>21.43</v>
       </c>
       <c r="H3">
         <v>8.4</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>8</v>
       </c>
       <c r="F4">
-        <v>77.78</v>
+        <v>76.19</v>
       </c>
       <c r="G4">
-        <v>22.22</v>
+        <v>19.05</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>8</v>
       </c>
       <c r="F5">
-        <v>80</v>
+        <v>77.78</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>22.22</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3925,7 +4004,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6">
         <v>33</v>
@@ -3957,7 +4036,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>34</v>
@@ -3991,7 +4070,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4000,16 +4079,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4020,22 +4099,102 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920145</v>
+        <v>19330051920436</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>19330051920436</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>19330051920393</v>
+      </c>
+      <c r="B4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>19330051920393</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>19330051920145</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4045,7 +4204,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4054,84 +4213,84 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920145</v>
+        <v>19330051920436</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>18330051920393</v>
+        <v>19330051920393</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920360</v>
+        <v>19330051920145</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920115</v>
+        <v>18330051920393</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -4139,16 +4298,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920116</v>
+        <v>19330051920360</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -4156,16 +4315,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920118</v>
+        <v>20330051920115</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -4173,16 +4332,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920121</v>
+        <v>20330051920116</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4190,16 +4349,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920427</v>
+        <v>20330051920118</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -4207,16 +4366,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920122</v>
+        <v>20330051920121</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -4224,16 +4383,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920123</v>
+        <v>19330051920427</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4241,16 +4400,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920124</v>
+        <v>20330051920122</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4258,16 +4417,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920125</v>
+        <v>20330051920123</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4275,16 +4434,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920126</v>
+        <v>20330051920124</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4292,16 +4451,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920127</v>
+        <v>20330051920125</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4309,16 +4468,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920128</v>
+        <v>20330051920126</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4326,16 +4485,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920129</v>
+        <v>20330051920127</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4343,16 +4502,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920131</v>
+        <v>20330051920128</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4360,16 +4519,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920132</v>
+        <v>20330051920129</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4377,16 +4536,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920133</v>
+        <v>20330051920131</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4394,16 +4553,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920134</v>
+        <v>20330051920132</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4411,16 +4570,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920135</v>
+        <v>20330051920133</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4428,16 +4587,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920136</v>
+        <v>20330051920134</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4445,16 +4604,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920137</v>
+        <v>20330051920135</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4462,16 +4621,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920383</v>
+        <v>20330051920136</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4479,16 +4638,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920139</v>
+        <v>20330051920137</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4496,16 +4655,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920387</v>
+        <v>19330051920383</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4513,16 +4672,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920140</v>
+        <v>20330051920139</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4530,16 +4689,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920141</v>
+        <v>19330051920387</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4547,16 +4706,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920389</v>
+        <v>20330051920140</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4564,16 +4723,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920142</v>
+        <v>20330051920141</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4581,16 +4740,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920143</v>
+        <v>20330051920389</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D32" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -4598,16 +4757,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920144</v>
+        <v>20330051920142</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -4615,16 +4774,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920387</v>
+        <v>20330051920143</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D34" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -4632,16 +4791,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>18330051920185</v>
+        <v>20330051920144</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -4649,13 +4808,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920148</v>
+        <v>20330051920387</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D36" t="s">
         <v>166</v>
@@ -4666,16 +4825,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>20330051920150</v>
+        <v>18330051920185</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -4683,16 +4842,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>20330051920151</v>
+        <v>20330051920148</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D38" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -4700,13 +4859,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>20330051920153</v>
+        <v>20330051920150</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>109</v>
+      </c>
+      <c r="C39" t="s">
+        <v>139</v>
       </c>
       <c r="D39" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -4714,16 +4876,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>18330051920189</v>
+        <v>20330051920151</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="D40" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -4731,18 +4893,49 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
+        <v>20330051920153</v>
+      </c>
+      <c r="B41" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>18330051920189</v>
+      </c>
+      <c r="B42" t="s">
+        <v>112</v>
+      </c>
+      <c r="C42" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" t="s">
+        <v>177</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
         <v>19330051920399</v>
       </c>
-      <c r="B41" t="s">
-        <v>105</v>
-      </c>
-      <c r="C41" t="s">
-        <v>134</v>
-      </c>
-      <c r="D41" t="s">
-        <v>171</v>
-      </c>
-      <c r="E41">
+      <c r="B43" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43" t="s">
+        <v>141</v>
+      </c>
+      <c r="D43" t="s">
+        <v>178</v>
+      </c>
+      <c r="E43">
         <v>0</v>
       </c>
     </row>
@@ -4753,7 +4946,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4762,22 +4955,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -4788,19 +4981,19 @@
         <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4811,19 +5004,19 @@
         <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4831,93 +5024,185 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920116</v>
+        <v>19330051920436</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920123</v>
+        <v>19330051920436</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920133</v>
+        <v>19330051920393</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
+        <v>19330051920393</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920116</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920123</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
         <v>19330051920399</v>
       </c>
-      <c r="B7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7">
+      <c r="B11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20221.xlsx
+++ b/grupos/5ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="179">
   <si>
     <t>Materia</t>
   </si>
@@ -1058,19 +1058,19 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -1093,7 +1093,7 @@
         <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1152,13 +1152,13 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1170,13 +1170,13 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>9</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1229,13 +1229,13 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1306,13 +1306,13 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1324,7 +1324,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1383,13 +1383,13 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1401,13 +1401,13 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1460,13 +1460,13 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1478,13 +1478,13 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>9</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1537,13 +1537,13 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1555,13 +1555,13 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1614,13 +1614,13 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1691,13 +1691,13 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1715,7 +1715,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1768,13 +1768,13 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1845,13 +1845,13 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1922,13 +1922,13 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1999,13 +1999,13 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2017,13 +2017,13 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2076,13 +2076,13 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2153,13 +2153,13 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2230,13 +2230,13 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2248,13 +2248,13 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2307,13 +2307,13 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2384,13 +2384,13 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2402,13 +2402,13 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2461,13 +2461,13 @@
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2538,13 +2538,13 @@
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2615,13 +2615,13 @@
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2633,7 +2633,7 @@
         <v>6</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2692,13 +2692,13 @@
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2710,13 +2710,13 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>8</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2745,19 +2745,19 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2810,13 +2810,13 @@
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2887,13 +2887,13 @@
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -2905,7 +2905,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -2964,13 +2964,13 @@
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -2982,13 +2982,13 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>10</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -3041,13 +3041,13 @@
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3059,7 +3059,7 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3118,13 +3118,13 @@
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3224,13 +3224,13 @@
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3301,13 +3301,13 @@
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3319,7 +3319,7 @@
         <v>7</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>10</v>
@@ -3407,13 +3407,13 @@
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3431,7 +3431,7 @@
         <v>9</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -3454,13 +3454,13 @@
         <v>6</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
         <v>-1</v>
       </c>
       <c r="X38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>7</v>
@@ -3513,13 +3513,13 @@
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q39">
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -3531,13 +3531,13 @@
         <v>7</v>
       </c>
       <c r="V39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W39">
         <v>9</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>8</v>
@@ -3590,13 +3590,13 @@
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -3667,13 +3667,13 @@
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q41">
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -3714,7 +3714,7 @@
         <v>5</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S42">
         <v>-1</v>
@@ -3767,10 +3767,10 @@
         <v>-1</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S43">
         <v>-1</v>
@@ -3808,7 +3808,7 @@
         <v>5</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S44">
         <v>-1</v>
@@ -3914,19 +3914,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>73.81</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="G3">
-        <v>21.43</v>
+        <v>23.81</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -3990,7 +3990,7 @@
         <v>22.22</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4946,7 +4946,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5185,24 +5185,47 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
+        <v>19330051920383</v>
+      </c>
+      <c r="B11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
         <v>19330051920399</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>113</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>141</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>178</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
         <v>64</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20221.xlsx
+++ b/grupos/5ARHV - Estadisticos 20221.xlsx
@@ -1155,7 +1155,7 @@
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
         <v>6</v>
@@ -1173,7 +1173,7 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1232,7 +1232,7 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -1309,7 +1309,7 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -1386,7 +1386,7 @@
         <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>6</v>
@@ -1404,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1463,7 +1463,7 @@
         <v>4</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>5</v>
@@ -1481,7 +1481,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1540,7 +1540,7 @@
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <v>4</v>
@@ -1694,7 +1694,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -1771,7 +1771,7 @@
         <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>9</v>
@@ -1848,7 +1848,7 @@
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>9</v>
@@ -1925,7 +1925,7 @@
         <v>4</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <v>4</v>
@@ -2002,7 +2002,7 @@
         <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -2020,7 +2020,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -2079,7 +2079,7 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>9</v>
@@ -2156,7 +2156,7 @@
         <v>4</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>4</v>
@@ -2233,7 +2233,7 @@
         <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>8</v>
@@ -2251,7 +2251,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2310,7 +2310,7 @@
         <v>4</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>4</v>
@@ -2328,7 +2328,7 @@
         <v>5</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2387,7 +2387,7 @@
         <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
         <v>6</v>
@@ -2464,7 +2464,7 @@
         <v>4</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
         <v>4</v>
@@ -2482,7 +2482,7 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2541,7 +2541,7 @@
         <v>4</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>4</v>
@@ -2559,7 +2559,7 @@
         <v>5</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2618,7 +2618,7 @@
         <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -2695,7 +2695,7 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <v>8</v>
@@ -2713,7 +2713,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2813,7 +2813,7 @@
         <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>9</v>
@@ -2890,7 +2890,7 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
         <v>10</v>
@@ -2967,7 +2967,7 @@
         <v>4</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>8</v>
@@ -3044,7 +3044,7 @@
         <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
         <v>9</v>
@@ -3121,7 +3121,7 @@
         <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -3227,7 +3227,7 @@
         <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -3304,7 +3304,7 @@
         <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>9</v>
@@ -3410,7 +3410,7 @@
         <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>8</v>
@@ -3428,7 +3428,7 @@
         <v>6</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X37">
         <v>9</v>
@@ -3516,7 +3516,7 @@
         <v>4</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R39">
         <v>4</v>
@@ -3534,7 +3534,7 @@
         <v>6</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>10</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>10</v>
@@ -3670,7 +3670,7 @@
         <v>4</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R41">
         <v>4</v>
@@ -4010,19 +4010,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>87.88</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G6">
-        <v>12.12</v>
+        <v>15.15</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/5ARHV - Estadisticos 20221.xlsx
+++ b/grupos/5ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="179">
   <si>
     <t>Materia</t>
   </si>
@@ -206,16 +206,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>Molina Quezada Raúl</t>
@@ -1064,7 +1064,7 @@
         <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1096,7 +1096,7 @@
         <v>4</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -1146,10 +1146,10 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>5</v>
@@ -1161,13 +1161,13 @@
         <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>9</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1179,7 +1179,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1223,10 +1223,10 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>8</v>
@@ -1238,13 +1238,13 @@
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>9</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1256,7 +1256,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1300,10 +1300,10 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>8</v>
@@ -1315,13 +1315,13 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1377,10 +1377,10 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -1392,13 +1392,13 @@
         <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1454,10 +1454,10 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>4</v>
@@ -1469,10 +1469,10 @@
         <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1487,7 +1487,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1531,10 +1531,10 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>7</v>
@@ -1546,7 +1546,7 @@
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1608,10 +1608,10 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>4</v>
@@ -1623,7 +1623,7 @@
         <v>4</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -1685,10 +1685,10 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>8</v>
@@ -1700,13 +1700,13 @@
         <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1762,10 +1762,10 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>7</v>
@@ -1777,7 +1777,7 @@
         <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -1854,7 +1854,7 @@
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1916,10 +1916,10 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>4</v>
@@ -1931,13 +1931,13 @@
         <v>4</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -1993,10 +1993,10 @@
         <v>4</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -2008,13 +2008,13 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -2070,10 +2070,10 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>8</v>
@@ -2085,13 +2085,13 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>9</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -2147,10 +2147,10 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>4</v>
@@ -2162,10 +2162,10 @@
         <v>4</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -2224,10 +2224,10 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -2239,13 +2239,13 @@
         <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>9</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2257,7 +2257,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2301,10 +2301,10 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>4</v>
@@ -2316,13 +2316,13 @@
         <v>4</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2378,10 +2378,10 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
         <v>6</v>
@@ -2393,13 +2393,13 @@
         <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2411,7 +2411,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2455,10 +2455,10 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>4</v>
@@ -2470,10 +2470,10 @@
         <v>4</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>5</v>
@@ -2532,10 +2532,10 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>4</v>
@@ -2547,13 +2547,13 @@
         <v>4</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2609,10 +2609,10 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>6</v>
@@ -2624,13 +2624,13 @@
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -2642,7 +2642,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2686,10 +2686,10 @@
         <v>4</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>8</v>
@@ -2701,10 +2701,10 @@
         <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>9</v>
@@ -2751,7 +2751,7 @@
         <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -2804,10 +2804,10 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>6</v>
@@ -2819,7 +2819,7 @@
         <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -2881,10 +2881,10 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
         <v>7</v>
@@ -2896,7 +2896,7 @@
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2914,7 +2914,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2958,10 +2958,10 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>4</v>
@@ -2973,13 +2973,13 @@
         <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>6</v>
@@ -3035,10 +3035,10 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>7</v>
@@ -3050,13 +3050,13 @@
         <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>9</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3112,10 +3112,10 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>10</v>
@@ -3127,7 +3127,7 @@
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3218,10 +3218,10 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>10</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3295,10 +3295,10 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
         <v>7</v>
@@ -3310,13 +3310,13 @@
         <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3328,7 +3328,7 @@
         <v>9</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3401,10 +3401,10 @@
         <v>4</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
         <v>6</v>
@@ -3416,10 +3416,10 @@
         <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U37">
         <v>6</v>
@@ -3457,7 +3457,7 @@
         <v>9</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>9</v>
@@ -3507,10 +3507,10 @@
         <v>7</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
         <v>4</v>
@@ -3522,13 +3522,13 @@
         <v>4</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
         <v>10</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>6</v>
@@ -3584,10 +3584,10 @@
         <v>9</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P40">
         <v>10</v>
@@ -3599,7 +3599,7 @@
         <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
         <v>10</v>
@@ -3661,10 +3661,10 @@
         <v>5</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P41">
         <v>4</v>
@@ -3679,7 +3679,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U41">
         <v>5</v>
@@ -3717,13 +3717,13 @@
         <v>8</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X42">
         <v>9</v>
       </c>
       <c r="Y42">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -3764,7 +3764,7 @@
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P43">
         <v>4</v>
@@ -3773,7 +3773,7 @@
         <v>4</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T43">
         <v>-1</v>
@@ -3873,39 +3873,39 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>67.65000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="G2">
-        <v>32.35</v>
+        <v>23.81</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -3914,19 +3914,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>71.43000000000001</v>
+        <v>76.19</v>
       </c>
       <c r="G3">
-        <v>23.81</v>
+        <v>19.05</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -3937,60 +3937,60 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E4">
         <v>8</v>
       </c>
       <c r="F4">
-        <v>76.19</v>
+        <v>77.78</v>
       </c>
       <c r="G4">
-        <v>19.05</v>
+        <v>22.22</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>28</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>77.78</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G5">
-        <v>22.22</v>
+        <v>15.15</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4001,28 +4001,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6">
-        <v>84.84999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G6">
-        <v>15.15</v>
+        <v>14.71</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4042,19 +4042,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>94.12</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G7">
-        <v>2.94</v>
+        <v>8.82</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -4114,7 +4114,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4134,7 +4134,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4154,7 +4154,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4174,7 +4174,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4946,7 +4946,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4993,7 +4993,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5016,7 +5016,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5039,7 +5039,7 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5062,7 +5062,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5085,7 +5085,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5108,7 +5108,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -5116,19 +5116,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920116</v>
+        <v>19330051920383</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>62</v>
@@ -5139,93 +5139,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920123</v>
+        <v>19330051920399</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920133</v>
-      </c>
-      <c r="B10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920383</v>
-      </c>
-      <c r="B11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920399</v>
-      </c>
-      <c r="B12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" t="s">
-        <v>141</v>
-      </c>
-      <c r="D12" t="s">
-        <v>178</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20221.xlsx
+++ b/grupos/5ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="179">
   <si>
     <t>Materia</t>
   </si>
@@ -209,15 +209,15 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
@@ -233,325 +233,325 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CONGUILLO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>FERNANDEZ</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>QUIAHUA</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PAZOS</t>
+  </si>
+  <si>
     <t>ESPINOSA</t>
   </si>
   <si>
+    <t>VERGEL</t>
+  </si>
+  <si>
+    <t>TANIA</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>CONSUELO DALILA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>VALENTIN</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>SANDY SAMARA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>TAILY</t>
+  </si>
+  <si>
     <t>ASTRID</t>
   </si>
   <si>
+    <t>INGRID YALITH</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
     <t>ITZEL ISABEL</t>
   </si>
   <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>DIANA VIANNEY</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>CARLA DANIELA</t>
+  </si>
+  <si>
     <t>JARED JESUS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PAZOS</t>
-  </si>
-  <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
-    <t>TANIA</t>
-  </si>
-  <si>
-    <t>AMYRA NAHOMY</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>VALENTIN</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>IVAN DE JESUS</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
-    <t>INGRID YALITH</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>DIANA VIANNEY</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>CARLA DANIELA</t>
   </si>
   <si>
     <t>PAULINA</t>
@@ -3153,28 +3153,28 @@
         <v>41</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3336,28 +3336,28 @@
         <v>44</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3676,7 +3676,7 @@
         <v>4</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T41">
         <v>6</v>
@@ -3694,7 +3694,7 @@
         <v>5</v>
       </c>
       <c r="Y41">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3731,7 +3731,7 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -3746,7 +3746,7 @@
         <v>5</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I43">
         <v>5</v>
@@ -3761,7 +3761,7 @@
         <v>5</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>5</v>
@@ -3776,7 +3776,7 @@
         <v>5</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U43">
         <v>5</v>
@@ -3811,13 +3811,13 @@
         <v>6</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X44">
         <v>7</v>
       </c>
       <c r="Y44">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3882,83 +3882,83 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>71.43000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="G2">
-        <v>23.81</v>
+        <v>26.19</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="F3">
-        <v>76.19</v>
+        <v>77.78</v>
       </c>
       <c r="G3">
-        <v>19.05</v>
+        <v>22.22</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>28</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>77.78</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G4">
-        <v>22.22</v>
+        <v>15.15</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3969,28 +3969,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5">
-        <v>84.84999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G5">
-        <v>15.15</v>
+        <v>14.71</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4001,28 +4001,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>85.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G6">
-        <v>14.71</v>
+        <v>14.29</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4045,22 +4045,22 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>88.23999999999999</v>
       </c>
       <c r="G7">
-        <v>8.82</v>
+        <v>11.76</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4070,7 +4070,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4095,106 +4095,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920436</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920436</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920393</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920393</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920145</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4230,64 +4130,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920436</v>
+        <v>18330051920393</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920393</v>
+        <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920145</v>
+        <v>20330051920115</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>18330051920393</v>
+        <v>20330051920116</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
         <v>142</v>
@@ -4298,13 +4198,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920360</v>
+        <v>20330051920118</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>143</v>
@@ -4315,13 +4215,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920115</v>
+        <v>20330051920121</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
         <v>144</v>
@@ -4332,13 +4232,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920116</v>
+        <v>19330051920427</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
         <v>145</v>
@@ -4349,13 +4249,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920118</v>
+        <v>20330051920122</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
         <v>146</v>
@@ -4366,13 +4266,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920121</v>
+        <v>20330051920123</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
         <v>147</v>
@@ -4383,13 +4283,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920427</v>
+        <v>20330051920124</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
         <v>148</v>
@@ -4400,13 +4300,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920122</v>
+        <v>20330051920125</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
         <v>149</v>
@@ -4417,13 +4317,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920123</v>
+        <v>20330051920126</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
         <v>150</v>
@@ -4434,13 +4334,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920124</v>
+        <v>20330051920127</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>151</v>
@@ -4451,13 +4351,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920125</v>
+        <v>20330051920128</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
         <v>152</v>
@@ -4468,13 +4368,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920126</v>
+        <v>20330051920129</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
         <v>153</v>
@@ -4485,13 +4385,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920127</v>
+        <v>20330051920131</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
         <v>154</v>
@@ -4502,13 +4402,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920128</v>
+        <v>20330051920132</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D18" t="s">
         <v>155</v>
@@ -4519,13 +4419,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920129</v>
+        <v>20330051920133</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
         <v>156</v>
@@ -4536,13 +4436,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920131</v>
+        <v>20330051920134</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
         <v>157</v>
@@ -4553,16 +4453,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920132</v>
+        <v>20330051920135</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4570,16 +4470,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920133</v>
+        <v>20330051920136</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4587,16 +4487,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920134</v>
+        <v>20330051920137</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4604,16 +4504,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920135</v>
+        <v>19330051920383</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4621,13 +4521,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920136</v>
+        <v>20330051920139</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
         <v>161</v>
@@ -4638,13 +4538,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920137</v>
+        <v>19330051920387</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
         <v>162</v>
@@ -4655,13 +4555,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920383</v>
+        <v>20330051920140</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
         <v>163</v>
@@ -4672,13 +4572,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920139</v>
+        <v>20330051920141</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s">
         <v>164</v>
@@ -4689,13 +4589,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920387</v>
+        <v>20330051920389</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
         <v>165</v>
@@ -4706,10 +4606,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920140</v>
+        <v>19330051920436</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
         <v>128</v>
@@ -4723,13 +4623,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920141</v>
+        <v>20330051920142</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
         <v>167</v>
@@ -4740,13 +4640,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920389</v>
+        <v>20330051920143</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
         <v>168</v>
@@ -4757,13 +4657,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920142</v>
+        <v>20330051920144</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
         <v>169</v>
@@ -4774,13 +4674,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920143</v>
+        <v>19330051920393</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
         <v>170</v>
@@ -4791,16 +4691,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920144</v>
+        <v>20330051920387</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -4808,16 +4708,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920387</v>
+        <v>18330051920185</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -4825,13 +4725,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>18330051920185</v>
+        <v>20330051920148</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
         <v>172</v>
@@ -4842,13 +4742,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>20330051920148</v>
+        <v>20330051920150</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
         <v>173</v>
@@ -4859,13 +4759,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>20330051920150</v>
+        <v>20330051920151</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C39" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
         <v>174</v>
@@ -4876,13 +4776,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>20330051920151</v>
+        <v>20330051920153</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
-      </c>
-      <c r="C40" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D40" t="s">
         <v>175</v>
@@ -4893,10 +4790,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>20330051920153</v>
+        <v>18330051920189</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>105</v>
+      </c>
+      <c r="C41" t="s">
+        <v>136</v>
       </c>
       <c r="D41" t="s">
         <v>176</v>
@@ -4907,13 +4807,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>18330051920189</v>
+        <v>19330051920145</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
         <v>177</v>
@@ -4927,10 +4827,10 @@
         <v>19330051920399</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D43" t="s">
         <v>178</v>
@@ -4946,7 +4846,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4981,13 +4881,13 @@
         <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -5004,19 +4904,19 @@
         <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5024,16 +4924,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920436</v>
+        <v>19330051920383</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -5042,7 +4942,7 @@
         <v>62</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5050,113 +4950,21 @@
         <v>19330051920436</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920393</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920393</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920383</v>
-      </c>
-      <c r="B8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" t="s">
-        <v>163</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920399</v>
-      </c>
-      <c r="B9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>
